--- a/Documentacion/Hsitorias_Usuario.xlsx
+++ b/Documentacion/Hsitorias_Usuario.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50178dff44962c00/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50178dff44962c00/Escritorio/Software_Inventario/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{024A3739-BD07-4726-8C07-DF826A3E652A}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{017E7C52-EBB3-40FA-AD83-F4AEE0423788}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -386,7 +386,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -514,6 +514,12 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
@@ -687,7 +693,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -729,9 +735,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -787,6 +790,108 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -808,112 +913,16 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1682,32 +1691,32 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="76"/>
-      <c r="F4" s="16" t="s">
+      <c r="E4" s="35"/>
+      <c r="F4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="16" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="1"/>
@@ -1718,25 +1727,25 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="37" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="13">
         <v>1</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="39" t="s">
         <v>105</v>
       </c>
       <c r="I5" s="1"/>
@@ -1747,17 +1756,17 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="72"/>
-      <c r="C6" s="74"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="38"/>
       <c r="D6" s="13">
         <v>2</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="77"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="39"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1766,17 +1775,17 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="72"/>
-      <c r="C7" s="74"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="38"/>
       <c r="D7" s="13">
         <v>3</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="77"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="39"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1785,17 +1794,17 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="72"/>
-      <c r="C8" s="74"/>
+      <c r="B8" s="36"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="13">
         <v>4</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="77"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1804,17 +1813,17 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="72"/>
-      <c r="C9" s="74"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="13">
         <v>5</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="77"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="39"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1823,13 +1832,13 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="22"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="21"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1838,25 +1847,25 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="37" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="13">
         <v>1</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="72" t="s">
+      <c r="G11" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="54" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1"/>
@@ -1867,17 +1876,17 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="71"/>
-      <c r="C12" s="74"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="38"/>
       <c r="D12" s="13">
         <v>2</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="78" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="69"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1886,17 +1895,17 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="71"/>
-      <c r="C13" s="74"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="38"/>
       <c r="D13" s="13">
         <v>3</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="72"/>
-      <c r="H13" s="69"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="55"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1905,17 +1914,17 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="71"/>
-      <c r="C14" s="74"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="38"/>
       <c r="D14" s="13">
         <v>4</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="72"/>
-      <c r="H14" s="69"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="55"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1924,17 +1933,17 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="71"/>
-      <c r="C15" s="74"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="38"/>
       <c r="D15" s="13">
         <v>5</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="72"/>
-      <c r="H15" s="69"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="55"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1943,23 +1952,23 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="71"/>
-      <c r="C16" s="73" t="s">
+      <c r="B16" s="41"/>
+      <c r="C16" s="37" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="13">
         <v>1</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="78" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="69"/>
+      <c r="H16" s="55"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1968,17 +1977,17 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="71"/>
-      <c r="C17" s="73"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="37"/>
       <c r="D17" s="13">
         <v>2</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="63"/>
-      <c r="H17" s="69"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="55"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1987,17 +1996,17 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="71"/>
-      <c r="C18" s="73"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="37"/>
       <c r="D18" s="13">
         <v>3</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="69"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="55"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -2006,17 +2015,17 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="71"/>
-      <c r="C19" s="73"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="37"/>
       <c r="D19" s="13">
         <v>4</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="69"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="55"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -2025,17 +2034,17 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="71"/>
-      <c r="C20" s="73"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="37"/>
       <c r="D20" s="13">
         <v>5</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="78" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="64"/>
-      <c r="H20" s="69"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="55"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -2044,23 +2053,23 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="71"/>
-      <c r="C21" s="46" t="s">
+      <c r="B21" s="41"/>
+      <c r="C21" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="13">
         <v>1</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="65" t="s">
+      <c r="G21" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="69"/>
+      <c r="H21" s="55"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -2069,17 +2078,17 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="71"/>
-      <c r="C22" s="46"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="47"/>
       <c r="D22" s="13">
         <v>2</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="69"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="55"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2088,17 +2097,17 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="71"/>
-      <c r="C23" s="46"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="47"/>
       <c r="D23" s="13">
         <v>3</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="78" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="42"/>
-      <c r="G23" s="67"/>
-      <c r="H23" s="69"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="55"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2107,23 +2116,23 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="2:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="71"/>
+      <c r="B24" s="41"/>
       <c r="C24" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D24" s="13">
         <v>1</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="78" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="70"/>
+      <c r="H24" s="56"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2132,13 +2141,13 @@
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="2:14" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="30"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="29"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -2147,10 +2156,10 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="47" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="13">
@@ -2159,13 +2168,13 @@
       <c r="E26" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="F26" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="60" t="s">
+      <c r="G26" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="47" t="s">
+      <c r="H26" s="42" t="s">
         <v>58</v>
       </c>
       <c r="I26" s="1"/>
@@ -2176,17 +2185,17 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:14" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="51"/>
-      <c r="C27" s="46"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="47"/>
       <c r="D27" s="13">
         <v>2</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="42"/>
-      <c r="G27" s="60"/>
-      <c r="H27" s="48"/>
+      <c r="F27" s="40"/>
+      <c r="G27" s="45"/>
+      <c r="H27" s="43"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2195,17 +2204,17 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="51"/>
-      <c r="C28" s="46"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="47"/>
       <c r="D28" s="13">
         <v>3</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="48"/>
+      <c r="F28" s="40"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="43"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2214,30 +2223,30 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="2:14" s="4" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="51"/>
-      <c r="C29" s="46"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="47"/>
       <c r="D29" s="13">
         <v>4</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="42"/>
-      <c r="G29" s="60"/>
-      <c r="H29" s="48"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="45"/>
+      <c r="H29" s="43"/>
     </row>
     <row r="30" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="51"/>
-      <c r="C30" s="46"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="47"/>
       <c r="D30" s="13">
         <v>5</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="42"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="48"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="43"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2246,8 +2255,8 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="2:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="51"/>
-      <c r="C31" s="46" t="s">
+      <c r="B31" s="57"/>
+      <c r="C31" s="47" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="13">
@@ -2256,13 +2265,13 @@
       <c r="E31" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="42" t="s">
+      <c r="F31" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="50" t="s">
+      <c r="G31" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="48"/>
+      <c r="H31" s="43"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2271,17 +2280,17 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="51"/>
-      <c r="C32" s="46"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="47"/>
       <c r="D32" s="13">
         <v>2</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="48"/>
+      <c r="F32" s="40"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="43"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2290,17 +2299,17 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="51"/>
-      <c r="C33" s="46"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="47"/>
       <c r="D33" s="13">
         <v>3</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="42"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="48"/>
+      <c r="F33" s="40"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="43"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2309,17 +2318,17 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="51"/>
-      <c r="C34" s="46"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="47"/>
       <c r="D34" s="13">
         <v>4</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="42"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="48"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="43"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2328,8 +2337,8 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="51"/>
-      <c r="C35" s="46" t="s">
+      <c r="B35" s="57"/>
+      <c r="C35" s="47" t="s">
         <v>109</v>
       </c>
       <c r="D35" s="13">
@@ -2338,13 +2347,13 @@
       <c r="E35" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="42" t="s">
+      <c r="F35" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="50" t="s">
+      <c r="G35" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="48"/>
+      <c r="H35" s="43"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2353,17 +2362,17 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="51"/>
-      <c r="C36" s="46"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="47"/>
       <c r="D36" s="13">
         <v>2</v>
       </c>
       <c r="E36" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="42"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="48"/>
+      <c r="F36" s="40"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="43"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2372,17 +2381,17 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="51"/>
-      <c r="C37" s="46"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="47"/>
       <c r="D37" s="13">
         <v>3</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="42"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="48"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="43"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2391,17 +2400,17 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="51"/>
-      <c r="C38" s="46"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="47"/>
       <c r="D38" s="13">
         <v>4</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="48"/>
+      <c r="F38" s="40"/>
+      <c r="G38" s="46"/>
+      <c r="H38" s="43"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2410,17 +2419,17 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="51"/>
-      <c r="C39" s="46"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="47"/>
       <c r="D39" s="13">
         <v>5</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="42"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="48"/>
+      <c r="F39" s="40"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="43"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2429,8 +2438,8 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="51"/>
-      <c r="C40" s="46" t="s">
+      <c r="B40" s="57"/>
+      <c r="C40" s="47" t="s">
         <v>40</v>
       </c>
       <c r="D40" s="13">
@@ -2439,13 +2448,13 @@
       <c r="E40" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="42" t="s">
+      <c r="F40" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="50" t="s">
+      <c r="G40" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="48"/>
+      <c r="H40" s="43"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2454,17 +2463,17 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="51"/>
-      <c r="C41" s="46"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="47"/>
       <c r="D41" s="13">
         <v>2</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="42"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="48"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="46"/>
+      <c r="H41" s="43"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2473,17 +2482,17 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="51"/>
-      <c r="C42" s="46"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="47"/>
       <c r="D42" s="13">
         <v>3</v>
       </c>
       <c r="E42" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="42"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="48"/>
+      <c r="F42" s="40"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="43"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2492,17 +2501,17 @@
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="51"/>
-      <c r="C43" s="46"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="47"/>
       <c r="D43" s="13">
         <v>4</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="48"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="46"/>
+      <c r="H43" s="43"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2511,17 +2520,17 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="51"/>
-      <c r="C44" s="46"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="47"/>
       <c r="D44" s="13">
         <v>5</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="42"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="49"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="46"/>
+      <c r="H44" s="44"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2530,13 +2539,13 @@
       <c r="N44" s="1"/>
     </row>
     <row r="45" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B45" s="25"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="24"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="31"/>
-      <c r="H45" s="30"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="29"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -2545,10 +2554,10 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="51" t="s">
+      <c r="B46" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="59" t="s">
+      <c r="C46" s="61" t="s">
         <v>60</v>
       </c>
       <c r="D46" s="13">
@@ -2557,13 +2566,13 @@
       <c r="E46" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="42" t="s">
+      <c r="F46" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="60" t="s">
+      <c r="G46" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="47" t="s">
+      <c r="H46" s="42" t="s">
         <v>70</v>
       </c>
       <c r="I46" s="1"/>
@@ -2574,17 +2583,17 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B47" s="51"/>
-      <c r="C47" s="59"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="61"/>
       <c r="D47" s="13">
         <v>2</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F47" s="42"/>
-      <c r="G47" s="60"/>
-      <c r="H47" s="48"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="43"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2593,17 +2602,17 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B48" s="51"/>
-      <c r="C48" s="59"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="61"/>
       <c r="D48" s="13">
         <v>3</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="42"/>
-      <c r="G48" s="60"/>
-      <c r="H48" s="48"/>
+      <c r="F48" s="40"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="43"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2612,17 +2621,17 @@
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B49" s="51"/>
-      <c r="C49" s="59"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="61"/>
       <c r="D49" s="13">
         <v>4</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="60"/>
-      <c r="H49" s="48"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="43"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2631,17 +2640,17 @@
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B50" s="51"/>
-      <c r="C50" s="59"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="61"/>
       <c r="D50" s="13">
         <v>5</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="43"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="48"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="43"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2650,23 +2659,23 @@
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="51"/>
-      <c r="C51" s="46" t="s">
+      <c r="B51" s="57"/>
+      <c r="C51" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="20">
+      <c r="D51" s="19">
         <v>1</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F51" s="42" t="s">
+      <c r="F51" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="56" t="s">
+      <c r="G51" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="48"/>
+      <c r="H51" s="43"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2675,17 +2684,17 @@
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B52" s="51"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="20">
+      <c r="B52" s="57"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="19">
         <v>2</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="42"/>
-      <c r="G52" s="57"/>
-      <c r="H52" s="48"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="43"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2694,17 +2703,17 @@
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B53" s="51"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="20">
+      <c r="B53" s="57"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="19">
         <v>3</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="42"/>
-      <c r="G53" s="57"/>
-      <c r="H53" s="48"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="43"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2713,17 +2722,17 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B54" s="51"/>
-      <c r="C54" s="46"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="47"/>
       <c r="D54" s="13">
         <v>4</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="42"/>
-      <c r="G54" s="57"/>
-      <c r="H54" s="48"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="43"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -2732,17 +2741,17 @@
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="51"/>
-      <c r="C55" s="46"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="47"/>
       <c r="D55" s="13">
         <v>5</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F55" s="42"/>
-      <c r="G55" s="58"/>
-      <c r="H55" s="49"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="60"/>
+      <c r="H55" s="44"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2751,13 +2760,13 @@
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B56" s="25"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="24"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="30"/>
+      <c r="B56" s="24"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="29"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -2766,10 +2775,10 @@
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="2:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="57" t="s">
         <v>71</v>
       </c>
-      <c r="C57" s="46" t="s">
+      <c r="C57" s="47" t="s">
         <v>72</v>
       </c>
       <c r="D57" s="13">
@@ -2778,13 +2787,13 @@
       <c r="E57" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="F57" s="52" t="s">
+      <c r="F57" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="50" t="s">
+      <c r="G57" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="H57" s="55" t="s">
+      <c r="H57" s="67" t="s">
         <v>88</v>
       </c>
       <c r="I57" s="1"/>
@@ -2795,17 +2804,17 @@
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="51"/>
-      <c r="C58" s="46"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="47"/>
       <c r="D58" s="13">
         <v>2</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="53"/>
-      <c r="G58" s="50"/>
-      <c r="H58" s="55"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="67"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2814,17 +2823,17 @@
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="51"/>
-      <c r="C59" s="46"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="47"/>
       <c r="D59" s="13">
         <v>3</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="F59" s="53"/>
-      <c r="G59" s="50"/>
-      <c r="H59" s="55"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="46"/>
+      <c r="H59" s="67"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2833,17 +2842,17 @@
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="2:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="51"/>
-      <c r="C60" s="46"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="47"/>
       <c r="D60" s="13">
         <v>4</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="F60" s="54"/>
-      <c r="G60" s="50"/>
-      <c r="H60" s="55"/>
+      <c r="F60" s="66"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="67"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2852,8 +2861,8 @@
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="51"/>
-      <c r="C61" s="46" t="s">
+      <c r="B61" s="57"/>
+      <c r="C61" s="47" t="s">
         <v>73</v>
       </c>
       <c r="D61" s="13">
@@ -2862,13 +2871,13 @@
       <c r="E61" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="F61" s="52" t="s">
+      <c r="F61" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="50" t="s">
+      <c r="G61" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H61" s="55"/>
+      <c r="H61" s="67"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2877,17 +2886,17 @@
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="51"/>
-      <c r="C62" s="46"/>
+      <c r="B62" s="57"/>
+      <c r="C62" s="47"/>
       <c r="D62" s="13">
         <v>2</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F62" s="53"/>
-      <c r="G62" s="50"/>
-      <c r="H62" s="55"/>
+      <c r="F62" s="65"/>
+      <c r="G62" s="46"/>
+      <c r="H62" s="67"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -2896,17 +2905,17 @@
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="2:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="51"/>
-      <c r="C63" s="46"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="47"/>
       <c r="D63" s="13">
         <v>3</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F63" s="53"/>
-      <c r="G63" s="50"/>
-      <c r="H63" s="55"/>
+      <c r="F63" s="65"/>
+      <c r="G63" s="46"/>
+      <c r="H63" s="67"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -2915,17 +2924,17 @@
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="2:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="51"/>
-      <c r="C64" s="46"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="47"/>
       <c r="D64" s="13">
         <v>4</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="54"/>
-      <c r="G64" s="50"/>
-      <c r="H64" s="55"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="46"/>
+      <c r="H64" s="67"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -2934,8 +2943,8 @@
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="51"/>
-      <c r="C65" s="46" t="s">
+      <c r="B65" s="57"/>
+      <c r="C65" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D65" s="13">
@@ -2944,13 +2953,13 @@
       <c r="E65" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="F65" s="52" t="s">
+      <c r="F65" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="50" t="s">
+      <c r="G65" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="55"/>
+      <c r="H65" s="67"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2959,17 +2968,17 @@
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B66" s="51"/>
-      <c r="C66" s="46"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="47"/>
       <c r="D66" s="13">
         <v>2</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="53"/>
-      <c r="G66" s="50"/>
-      <c r="H66" s="55"/>
+      <c r="F66" s="65"/>
+      <c r="G66" s="46"/>
+      <c r="H66" s="67"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2978,17 +2987,17 @@
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B67" s="51"/>
-      <c r="C67" s="46"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="47"/>
       <c r="D67" s="13">
         <v>3</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F67" s="53"/>
-      <c r="G67" s="50"/>
-      <c r="H67" s="55"/>
+      <c r="F67" s="65"/>
+      <c r="G67" s="46"/>
+      <c r="H67" s="67"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -2997,17 +3006,17 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="51"/>
-      <c r="C68" s="46"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="47"/>
       <c r="D68" s="13">
         <v>4</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F68" s="54"/>
-      <c r="G68" s="50"/>
-      <c r="H68" s="55"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="67"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -3016,8 +3025,8 @@
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="2:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="51"/>
-      <c r="C69" s="46" t="s">
+      <c r="B69" s="57"/>
+      <c r="C69" s="47" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="13">
@@ -3026,13 +3035,13 @@
       <c r="E69" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F69" s="42" t="s">
+      <c r="F69" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="G69" s="50" t="s">
+      <c r="G69" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="H69" s="55"/>
+      <c r="H69" s="67"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3041,17 +3050,17 @@
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B70" s="51"/>
-      <c r="C70" s="46"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="47"/>
       <c r="D70" s="13">
         <v>2</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F70" s="42"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="55"/>
+      <c r="F70" s="40"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="67"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3060,17 +3069,17 @@
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B71" s="51"/>
-      <c r="C71" s="46"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="47"/>
       <c r="D71" s="13">
         <v>3</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F71" s="42"/>
-      <c r="G71" s="50"/>
-      <c r="H71" s="55"/>
+      <c r="F71" s="40"/>
+      <c r="G71" s="46"/>
+      <c r="H71" s="67"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3079,32 +3088,32 @@
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="51"/>
-      <c r="C72" s="46"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="47"/>
       <c r="D72" s="13">
         <v>4</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="F72" s="42"/>
-      <c r="G72" s="50"/>
-      <c r="H72" s="55"/>
+      <c r="F72" s="40"/>
+      <c r="G72" s="46"/>
+      <c r="H72" s="67"/>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="24"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="23"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
     </row>
     <row r="74" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="41" t="s">
+      <c r="B74" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="C74" s="46" t="s">
+      <c r="C74" s="47" t="s">
         <v>90</v>
       </c>
       <c r="D74" s="13">
@@ -3113,45 +3122,45 @@
       <c r="E74" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F74" s="43" t="s">
+      <c r="F74" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="38" t="s">
+      <c r="G74" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="H74" s="35" t="s">
+      <c r="H74" s="68" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B75" s="42"/>
-      <c r="C75" s="46"/>
+      <c r="B75" s="40"/>
+      <c r="C75" s="47"/>
       <c r="D75" s="13">
         <v>2</v>
       </c>
       <c r="E75" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F75" s="44"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="36"/>
+      <c r="F75" s="75"/>
+      <c r="G75" s="72"/>
+      <c r="H75" s="69"/>
     </row>
     <row r="76" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B76" s="42"/>
-      <c r="C76" s="46"/>
+      <c r="B76" s="40"/>
+      <c r="C76" s="47"/>
       <c r="D76" s="13">
         <v>3</v>
       </c>
       <c r="E76" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F76" s="45"/>
-      <c r="G76" s="40"/>
-      <c r="H76" s="36"/>
+      <c r="F76" s="76"/>
+      <c r="G76" s="73"/>
+      <c r="H76" s="69"/>
     </row>
     <row r="77" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="42"/>
-      <c r="C77" s="46" t="s">
+      <c r="B77" s="40"/>
+      <c r="C77" s="47" t="s">
         <v>91</v>
       </c>
       <c r="D77" s="13">
@@ -3160,56 +3169,56 @@
       <c r="E77" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F77" s="43" t="s">
+      <c r="F77" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="38" t="s">
+      <c r="G77" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="H77" s="36"/>
+      <c r="H77" s="69"/>
     </row>
     <row r="78" spans="2:14" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="42"/>
-      <c r="C78" s="46"/>
+      <c r="B78" s="40"/>
+      <c r="C78" s="47"/>
       <c r="D78" s="13">
         <v>2</v>
       </c>
       <c r="E78" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F78" s="44"/>
-      <c r="G78" s="39"/>
-      <c r="H78" s="36"/>
+      <c r="F78" s="75"/>
+      <c r="G78" s="72"/>
+      <c r="H78" s="69"/>
     </row>
     <row r="79" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="42"/>
-      <c r="C79" s="46"/>
+      <c r="B79" s="40"/>
+      <c r="C79" s="47"/>
       <c r="D79" s="13">
         <v>3</v>
       </c>
       <c r="E79" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F79" s="44"/>
-      <c r="G79" s="39"/>
-      <c r="H79" s="36"/>
+      <c r="F79" s="75"/>
+      <c r="G79" s="72"/>
+      <c r="H79" s="69"/>
     </row>
     <row r="80" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B80" s="42"/>
-      <c r="C80" s="46"/>
+      <c r="B80" s="40"/>
+      <c r="C80" s="47"/>
       <c r="D80" s="13">
         <v>4</v>
       </c>
       <c r="E80" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F80" s="45"/>
-      <c r="G80" s="40"/>
-      <c r="H80" s="36"/>
+      <c r="F80" s="76"/>
+      <c r="G80" s="73"/>
+      <c r="H80" s="69"/>
     </row>
     <row r="81" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="42"/>
-      <c r="C81" s="46" t="s">
+      <c r="B81" s="40"/>
+      <c r="C81" s="47" t="s">
         <v>92</v>
       </c>
       <c r="D81" s="13">
@@ -3218,66 +3227,101 @@
       <c r="E81" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F81" s="43" t="s">
+      <c r="F81" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="38" t="s">
+      <c r="G81" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="H81" s="36"/>
+      <c r="H81" s="69"/>
     </row>
     <row r="82" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="42"/>
-      <c r="C82" s="46"/>
+      <c r="B82" s="40"/>
+      <c r="C82" s="47"/>
       <c r="D82" s="13">
         <v>2</v>
       </c>
       <c r="E82" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F82" s="44"/>
-      <c r="G82" s="39"/>
-      <c r="H82" s="36"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="72"/>
+      <c r="H82" s="69"/>
     </row>
     <row r="83" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B83" s="42"/>
-      <c r="C83" s="46"/>
+      <c r="B83" s="40"/>
+      <c r="C83" s="47"/>
       <c r="D83" s="13">
         <v>3</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="F83" s="44"/>
-      <c r="G83" s="39"/>
-      <c r="H83" s="36"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="72"/>
+      <c r="H83" s="69"/>
     </row>
     <row r="84" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B84" s="42"/>
-      <c r="C84" s="46"/>
+      <c r="B84" s="40"/>
+      <c r="C84" s="47"/>
       <c r="D84" s="13">
         <v>4</v>
       </c>
       <c r="E84" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F84" s="45"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="37"/>
+      <c r="F84" s="76"/>
+      <c r="G84" s="73"/>
+      <c r="H84" s="70"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="21"/>
+      <c r="B85" s="20"/>
       <c r="C85" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="F5:F9"/>
-    <mergeCell ref="G5:G9"/>
+    <mergeCell ref="H74:H84"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="G77:G80"/>
+    <mergeCell ref="G81:G84"/>
+    <mergeCell ref="B74:B84"/>
+    <mergeCell ref="F81:F84"/>
+    <mergeCell ref="F77:F80"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="H46:H55"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="B57:B72"/>
+    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="F65:F68"/>
+    <mergeCell ref="F69:F72"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="G65:G68"/>
+    <mergeCell ref="G69:G72"/>
+    <mergeCell ref="H57:H72"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="F46:F50"/>
+    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="B26:B44"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H11:H24"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C35:C39"/>
     <mergeCell ref="B11:B24"/>
     <mergeCell ref="H26:H44"/>
     <mergeCell ref="G26:G30"/>
@@ -3294,48 +3338,13 @@
     <mergeCell ref="C11:C15"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H11:H24"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="F51:F55"/>
-    <mergeCell ref="G51:G55"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="G46:G50"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="B26:B44"/>
-    <mergeCell ref="H46:H55"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="G57:G60"/>
-    <mergeCell ref="B57:B72"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="F61:F64"/>
-    <mergeCell ref="F57:F60"/>
-    <mergeCell ref="F65:F68"/>
-    <mergeCell ref="F69:F72"/>
-    <mergeCell ref="G61:G64"/>
-    <mergeCell ref="G65:G68"/>
-    <mergeCell ref="G69:G72"/>
-    <mergeCell ref="H57:H72"/>
-    <mergeCell ref="C61:C64"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="H74:H84"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="G77:G80"/>
-    <mergeCell ref="G81:G84"/>
-    <mergeCell ref="B74:B84"/>
-    <mergeCell ref="F81:F84"/>
-    <mergeCell ref="F77:F80"/>
-    <mergeCell ref="F74:F76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="G5:G9"/>
   </mergeCells>
   <conditionalFormatting sqref="F5">
     <cfRule type="containsText" dxfId="53" priority="68" operator="containsText" text="MEDIUM">

--- a/Documentacion/Hsitorias_Usuario.xlsx
+++ b/Documentacion/Hsitorias_Usuario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50178dff44962c00/Escritorio/Software_Inventario/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{017E7C52-EBB3-40FA-AD83-F4AEE0423788}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F56ED0F3-B3D1-4328-879E-5A20240BAFAD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2784,7 +2784,7 @@
       <c r="D57" s="13">
         <v>1</v>
       </c>
-      <c r="E57" s="14" t="s">
+      <c r="E57" s="77" t="s">
         <v>76</v>
       </c>
       <c r="F57" s="64" t="s">
@@ -2809,7 +2809,7 @@
       <c r="D58" s="13">
         <v>2</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" s="77" t="s">
         <v>77</v>
       </c>
       <c r="F58" s="65"/>
@@ -2828,7 +2828,7 @@
       <c r="D59" s="13">
         <v>3</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" s="77" t="s">
         <v>78</v>
       </c>
       <c r="F59" s="65"/>
@@ -2847,7 +2847,7 @@
       <c r="D60" s="13">
         <v>4</v>
       </c>
-      <c r="E60" s="14" t="s">
+      <c r="E60" s="77" t="s">
         <v>79</v>
       </c>
       <c r="F60" s="66"/>
@@ -2868,7 +2868,7 @@
       <c r="D61" s="13">
         <v>1</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="77" t="s">
         <v>103</v>
       </c>
       <c r="F61" s="64" t="s">

--- a/Documentacion/Hsitorias_Usuario.xlsx
+++ b/Documentacion/Hsitorias_Usuario.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50178dff44962c00/Escritorio/Software_Inventario/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F56ED0F3-B3D1-4328-879E-5A20240BAFAD}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{555E0851-B4CC-4AAA-8D83-19A708D5042A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -790,139 +790,139 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1691,13 +1691,13 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="16" t="s">
@@ -1706,10 +1706,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="35"/>
+      <c r="E4" s="77"/>
       <c r="F4" s="15" t="s">
         <v>2</v>
       </c>
@@ -1727,25 +1727,25 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="36" t="s">
+      <c r="B5" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="71" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="13">
         <v>1</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="36" t="s">
+      <c r="G5" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="39" t="s">
+      <c r="H5" s="78" t="s">
         <v>105</v>
       </c>
       <c r="I5" s="1"/>
@@ -1756,17 +1756,17 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="36"/>
-      <c r="C6" s="38"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="13">
         <v>2</v>
       </c>
-      <c r="E6" s="77" t="s">
+      <c r="E6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="39"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="78"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1775,17 +1775,17 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="36"/>
-      <c r="C7" s="38"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="13">
         <v>3</v>
       </c>
-      <c r="E7" s="77" t="s">
+      <c r="E7" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="39"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1794,17 +1794,17 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="36"/>
-      <c r="C8" s="38"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="13">
         <v>4</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="40"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="39"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="78"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1813,17 +1813,17 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="36"/>
-      <c r="C9" s="38"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="13">
         <v>5</v>
       </c>
-      <c r="E9" s="77" t="s">
+      <c r="E9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="39"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="78"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1847,25 +1847,25 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="71" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="13">
         <v>1</v>
       </c>
-      <c r="E11" s="78" t="s">
+      <c r="E11" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="40" t="s">
+      <c r="F11" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="54" t="s">
+      <c r="H11" s="66" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1"/>
@@ -1876,17 +1876,17 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="41"/>
-      <c r="C12" s="38"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="13">
         <v>2</v>
       </c>
-      <c r="E12" s="78" t="s">
+      <c r="E12" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="55"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1895,17 +1895,17 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="41"/>
-      <c r="C13" s="38"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="13">
         <v>3</v>
       </c>
-      <c r="E13" s="78" t="s">
+      <c r="E13" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="55"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="67"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1914,17 +1914,17 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="41"/>
-      <c r="C14" s="38"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="13">
         <v>4</v>
       </c>
-      <c r="E14" s="78" t="s">
+      <c r="E14" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="55"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="67"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1933,17 +1933,17 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="41"/>
-      <c r="C15" s="38"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="72"/>
       <c r="D15" s="13">
         <v>5</v>
       </c>
-      <c r="E15" s="78" t="s">
+      <c r="E15" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="55"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1952,23 +1952,23 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="41"/>
-      <c r="C16" s="37" t="s">
+      <c r="B16" s="69"/>
+      <c r="C16" s="71" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="13">
         <v>1</v>
       </c>
-      <c r="E16" s="78" t="s">
+      <c r="E16" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="48" t="s">
+      <c r="G16" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="55"/>
+      <c r="H16" s="67"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1977,17 +1977,17 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="41"/>
-      <c r="C17" s="37"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="71"/>
       <c r="D17" s="13">
         <v>2</v>
       </c>
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="55"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="67"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1996,17 +1996,17 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="41"/>
-      <c r="C18" s="37"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="71"/>
       <c r="D18" s="13">
         <v>3</v>
       </c>
-      <c r="E18" s="78" t="s">
+      <c r="E18" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="55"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="67"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -2015,17 +2015,17 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="41"/>
-      <c r="C19" s="37"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="71"/>
       <c r="D19" s="13">
         <v>4</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="55"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="67"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -2034,17 +2034,17 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="41"/>
-      <c r="C20" s="37"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="71"/>
       <c r="D20" s="13">
         <v>5</v>
       </c>
-      <c r="E20" s="78" t="s">
+      <c r="E20" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="55"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="67"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -2053,23 +2053,23 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="41"/>
+      <c r="B21" s="69"/>
       <c r="C21" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="13">
         <v>1</v>
       </c>
-      <c r="E21" s="78" t="s">
+      <c r="E21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="40" t="s">
+      <c r="F21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="51" t="s">
+      <c r="G21" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="55"/>
+      <c r="H21" s="67"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -2078,17 +2078,17 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="41"/>
+      <c r="B22" s="69"/>
       <c r="C22" s="47"/>
       <c r="D22" s="13">
         <v>2</v>
       </c>
-      <c r="E22" s="78" t="s">
+      <c r="E22" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="52"/>
-      <c r="H22" s="55"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="67"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2097,17 +2097,17 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="41"/>
+      <c r="B23" s="69"/>
       <c r="C23" s="47"/>
       <c r="D23" s="13">
         <v>3</v>
       </c>
-      <c r="E23" s="78" t="s">
+      <c r="E23" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="55"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="67"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2116,14 +2116,14 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="2:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="41"/>
+      <c r="B24" s="69"/>
       <c r="C24" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D24" s="13">
         <v>1</v>
       </c>
-      <c r="E24" s="78" t="s">
+      <c r="E24" s="35" t="s">
         <v>33</v>
       </c>
       <c r="F24" s="17" t="s">
@@ -2132,7 +2132,7 @@
       <c r="G24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="56"/>
+      <c r="H24" s="68"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2156,7 +2156,7 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="57" t="s">
+      <c r="B26" s="52" t="s">
         <v>37</v>
       </c>
       <c r="C26" s="47" t="s">
@@ -2165,16 +2165,16 @@
       <c r="D26" s="13">
         <v>1</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="45" t="s">
+      <c r="G26" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="42" t="s">
+      <c r="H26" s="48" t="s">
         <v>58</v>
       </c>
       <c r="I26" s="1"/>
@@ -2185,17 +2185,17 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:14" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="57"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="47"/>
       <c r="D27" s="13">
         <v>2</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="49"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2204,17 +2204,17 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="57"/>
+      <c r="B28" s="52"/>
       <c r="C28" s="47"/>
       <c r="D28" s="13">
         <v>3</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="45"/>
-      <c r="H28" s="43"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="49"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2223,30 +2223,30 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="2:14" s="4" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="57"/>
+      <c r="B29" s="52"/>
       <c r="C29" s="47"/>
       <c r="D29" s="13">
         <v>4</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="43"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="49"/>
     </row>
     <row r="30" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="57"/>
+      <c r="B30" s="52"/>
       <c r="C30" s="47"/>
       <c r="D30" s="13">
         <v>5</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="43"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="49"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2255,23 +2255,23 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="2:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="57"/>
+      <c r="B31" s="52"/>
       <c r="C31" s="47" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="13">
         <v>1</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="40" t="s">
+      <c r="F31" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="46" t="s">
+      <c r="G31" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="43"/>
+      <c r="H31" s="49"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2280,17 +2280,17 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="57"/>
+      <c r="B32" s="52"/>
       <c r="C32" s="47"/>
       <c r="D32" s="13">
         <v>2</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="40"/>
-      <c r="G32" s="46"/>
-      <c r="H32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="49"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2299,7 +2299,7 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="57"/>
+      <c r="B33" s="52"/>
       <c r="C33" s="47"/>
       <c r="D33" s="13">
         <v>3</v>
@@ -2307,9 +2307,9 @@
       <c r="E33" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="40"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="43"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="49"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2318,7 +2318,7 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="57"/>
+      <c r="B34" s="52"/>
       <c r="C34" s="47"/>
       <c r="D34" s="13">
         <v>4</v>
@@ -2326,9 +2326,9 @@
       <c r="E34" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="40"/>
-      <c r="G34" s="46"/>
-      <c r="H34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="49"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2337,23 +2337,23 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="57"/>
+      <c r="B35" s="52"/>
       <c r="C35" s="47" t="s">
         <v>109</v>
       </c>
       <c r="D35" s="13">
         <v>1</v>
       </c>
-      <c r="E35" s="14" t="s">
+      <c r="E35" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="40" t="s">
+      <c r="F35" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="46" t="s">
+      <c r="G35" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="43"/>
+      <c r="H35" s="49"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2362,17 +2362,17 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="57"/>
+      <c r="B36" s="52"/>
       <c r="C36" s="47"/>
       <c r="D36" s="13">
         <v>2</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="E36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="40"/>
-      <c r="G36" s="46"/>
-      <c r="H36" s="43"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="49"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2381,7 +2381,7 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="57"/>
+      <c r="B37" s="52"/>
       <c r="C37" s="47"/>
       <c r="D37" s="13">
         <v>3</v>
@@ -2389,9 +2389,9 @@
       <c r="E37" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="40"/>
-      <c r="G37" s="46"/>
-      <c r="H37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="49"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2400,7 +2400,7 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="57"/>
+      <c r="B38" s="52"/>
       <c r="C38" s="47"/>
       <c r="D38" s="13">
         <v>4</v>
@@ -2408,9 +2408,9 @@
       <c r="E38" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="40"/>
-      <c r="G38" s="46"/>
-      <c r="H38" s="43"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="49"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2419,7 +2419,7 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="57"/>
+      <c r="B39" s="52"/>
       <c r="C39" s="47"/>
       <c r="D39" s="13">
         <v>5</v>
@@ -2427,9 +2427,9 @@
       <c r="E39" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="40"/>
-      <c r="G39" s="46"/>
-      <c r="H39" s="43"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="49"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2438,7 +2438,7 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="57"/>
+      <c r="B40" s="52"/>
       <c r="C40" s="47" t="s">
         <v>40</v>
       </c>
@@ -2448,13 +2448,13 @@
       <c r="E40" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="40" t="s">
+      <c r="F40" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="46" t="s">
+      <c r="G40" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="43"/>
+      <c r="H40" s="49"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2463,7 +2463,7 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="57"/>
+      <c r="B41" s="52"/>
       <c r="C41" s="47"/>
       <c r="D41" s="13">
         <v>2</v>
@@ -2471,9 +2471,9 @@
       <c r="E41" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="40"/>
-      <c r="G41" s="46"/>
-      <c r="H41" s="43"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="49"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2482,7 +2482,7 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="57"/>
+      <c r="B42" s="52"/>
       <c r="C42" s="47"/>
       <c r="D42" s="13">
         <v>3</v>
@@ -2490,9 +2490,9 @@
       <c r="E42" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="40"/>
-      <c r="G42" s="46"/>
-      <c r="H42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="49"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2501,7 +2501,7 @@
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="57"/>
+      <c r="B43" s="52"/>
       <c r="C43" s="47"/>
       <c r="D43" s="13">
         <v>4</v>
@@ -2509,9 +2509,9 @@
       <c r="E43" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="F43" s="40"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="43"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="49"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2520,7 +2520,7 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="57"/>
+      <c r="B44" s="52"/>
       <c r="C44" s="47"/>
       <c r="D44" s="13">
         <v>5</v>
@@ -2528,9 +2528,9 @@
       <c r="E44" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="40"/>
-      <c r="G44" s="46"/>
-      <c r="H44" s="44"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="50"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2554,10 +2554,10 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="57" t="s">
+      <c r="B46" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="61" t="s">
+      <c r="C46" s="60" t="s">
         <v>60</v>
       </c>
       <c r="D46" s="13">
@@ -2566,13 +2566,13 @@
       <c r="E46" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="40" t="s">
+      <c r="F46" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="45" t="s">
+      <c r="G46" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="42" t="s">
+      <c r="H46" s="48" t="s">
         <v>70</v>
       </c>
       <c r="I46" s="1"/>
@@ -2583,17 +2583,17 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B47" s="57"/>
-      <c r="C47" s="61"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="60"/>
       <c r="D47" s="13">
         <v>2</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F47" s="40"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="43"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="49"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2602,17 +2602,17 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B48" s="57"/>
-      <c r="C48" s="61"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="60"/>
       <c r="D48" s="13">
         <v>3</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="40"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="43"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="49"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2621,17 +2621,17 @@
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B49" s="57"/>
-      <c r="C49" s="61"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="60"/>
       <c r="D49" s="13">
         <v>4</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="40"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="43"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="49"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2640,17 +2640,17 @@
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B50" s="57"/>
-      <c r="C50" s="61"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="60"/>
       <c r="D50" s="13">
         <v>5</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="62"/>
-      <c r="G50" s="63"/>
-      <c r="H50" s="43"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="49"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2659,7 +2659,7 @@
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="57"/>
+      <c r="B51" s="52"/>
       <c r="C51" s="47" t="s">
         <v>61</v>
       </c>
@@ -2669,13 +2669,13 @@
       <c r="E51" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F51" s="40" t="s">
+      <c r="F51" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="58" t="s">
+      <c r="G51" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="43"/>
+      <c r="H51" s="49"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2684,7 +2684,7 @@
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B52" s="57"/>
+      <c r="B52" s="52"/>
       <c r="C52" s="47"/>
       <c r="D52" s="19">
         <v>2</v>
@@ -2692,9 +2692,9 @@
       <c r="E52" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="40"/>
-      <c r="G52" s="59"/>
-      <c r="H52" s="43"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="49"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2703,7 +2703,7 @@
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B53" s="57"/>
+      <c r="B53" s="52"/>
       <c r="C53" s="47"/>
       <c r="D53" s="19">
         <v>3</v>
@@ -2711,9 +2711,9 @@
       <c r="E53" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="40"/>
-      <c r="G53" s="59"/>
-      <c r="H53" s="43"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="49"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2722,7 +2722,7 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B54" s="57"/>
+      <c r="B54" s="52"/>
       <c r="C54" s="47"/>
       <c r="D54" s="13">
         <v>4</v>
@@ -2730,9 +2730,9 @@
       <c r="E54" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="40"/>
-      <c r="G54" s="59"/>
-      <c r="H54" s="43"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="49"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -2741,7 +2741,7 @@
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="57"/>
+      <c r="B55" s="52"/>
       <c r="C55" s="47"/>
       <c r="D55" s="13">
         <v>5</v>
@@ -2749,9 +2749,9 @@
       <c r="E55" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F55" s="40"/>
-      <c r="G55" s="60"/>
-      <c r="H55" s="44"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="50"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2775,7 +2775,7 @@
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="2:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="57" t="s">
+      <c r="B57" s="52" t="s">
         <v>71</v>
       </c>
       <c r="C57" s="47" t="s">
@@ -2784,16 +2784,16 @@
       <c r="D57" s="13">
         <v>1</v>
       </c>
-      <c r="E57" s="77" t="s">
+      <c r="E57" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="F57" s="64" t="s">
+      <c r="F57" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="46" t="s">
+      <c r="G57" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="H57" s="67" t="s">
+      <c r="H57" s="56" t="s">
         <v>88</v>
       </c>
       <c r="I57" s="1"/>
@@ -2804,17 +2804,17 @@
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="57"/>
+      <c r="B58" s="52"/>
       <c r="C58" s="47"/>
       <c r="D58" s="13">
         <v>2</v>
       </c>
-      <c r="E58" s="77" t="s">
+      <c r="E58" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="65"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="67"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="56"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2823,17 +2823,17 @@
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="57"/>
+      <c r="B59" s="52"/>
       <c r="C59" s="47"/>
       <c r="D59" s="13">
         <v>3</v>
       </c>
-      <c r="E59" s="77" t="s">
+      <c r="E59" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="F59" s="65"/>
-      <c r="G59" s="46"/>
-      <c r="H59" s="67"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="56"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2842,17 +2842,17 @@
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="2:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="57"/>
+      <c r="B60" s="52"/>
       <c r="C60" s="47"/>
       <c r="D60" s="13">
         <v>4</v>
       </c>
-      <c r="E60" s="77" t="s">
+      <c r="E60" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="F60" s="66"/>
-      <c r="G60" s="46"/>
-      <c r="H60" s="67"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="51"/>
+      <c r="H60" s="56"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2861,23 +2861,23 @@
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="57"/>
+      <c r="B61" s="52"/>
       <c r="C61" s="47" t="s">
         <v>73</v>
       </c>
       <c r="D61" s="13">
         <v>1</v>
       </c>
-      <c r="E61" s="77" t="s">
+      <c r="E61" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="F61" s="64" t="s">
+      <c r="F61" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="46" t="s">
+      <c r="G61" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H61" s="67"/>
+      <c r="H61" s="56"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2886,17 +2886,17 @@
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="57"/>
+      <c r="B62" s="52"/>
       <c r="C62" s="47"/>
       <c r="D62" s="13">
         <v>2</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F62" s="65"/>
-      <c r="G62" s="46"/>
-      <c r="H62" s="67"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="51"/>
+      <c r="H62" s="56"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -2905,17 +2905,17 @@
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="2:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="57"/>
+      <c r="B63" s="52"/>
       <c r="C63" s="47"/>
       <c r="D63" s="13">
         <v>3</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="F63" s="65"/>
-      <c r="G63" s="46"/>
-      <c r="H63" s="67"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="51"/>
+      <c r="H63" s="56"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -2924,17 +2924,17 @@
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="2:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="57"/>
+      <c r="B64" s="52"/>
       <c r="C64" s="47"/>
       <c r="D64" s="13">
         <v>4</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="66"/>
-      <c r="G64" s="46"/>
-      <c r="H64" s="67"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="51"/>
+      <c r="H64" s="56"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -2943,23 +2943,23 @@
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="57"/>
+      <c r="B65" s="52"/>
       <c r="C65" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D65" s="13">
         <v>1</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E65" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="F65" s="64" t="s">
+      <c r="F65" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="46" t="s">
+      <c r="G65" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="67"/>
+      <c r="H65" s="56"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2968,17 +2968,17 @@
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B66" s="57"/>
+      <c r="B66" s="52"/>
       <c r="C66" s="47"/>
       <c r="D66" s="13">
         <v>2</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="65"/>
-      <c r="G66" s="46"/>
-      <c r="H66" s="67"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="51"/>
+      <c r="H66" s="56"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2987,17 +2987,17 @@
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B67" s="57"/>
+      <c r="B67" s="52"/>
       <c r="C67" s="47"/>
       <c r="D67" s="13">
         <v>3</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E67" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="F67" s="65"/>
-      <c r="G67" s="46"/>
-      <c r="H67" s="67"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="56"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -3006,17 +3006,17 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="57"/>
+      <c r="B68" s="52"/>
       <c r="C68" s="47"/>
       <c r="D68" s="13">
         <v>4</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F68" s="66"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="67"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="56"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -3025,23 +3025,23 @@
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="2:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="57"/>
+      <c r="B69" s="52"/>
       <c r="C69" s="47" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="13">
         <v>1</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="F69" s="40" t="s">
+      <c r="F69" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G69" s="46" t="s">
+      <c r="G69" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H69" s="67"/>
+      <c r="H69" s="56"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3050,17 +3050,17 @@
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B70" s="57"/>
+      <c r="B70" s="52"/>
       <c r="C70" s="47"/>
       <c r="D70" s="13">
         <v>2</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="F70" s="40"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="67"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="56"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3069,17 +3069,17 @@
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B71" s="57"/>
+      <c r="B71" s="52"/>
       <c r="C71" s="47"/>
       <c r="D71" s="13">
         <v>3</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="F71" s="40"/>
-      <c r="G71" s="46"/>
-      <c r="H71" s="67"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="56"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3088,17 +3088,17 @@
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="57"/>
+      <c r="B72" s="52"/>
       <c r="C72" s="47"/>
       <c r="D72" s="13">
         <v>4</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E72" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F72" s="40"/>
-      <c r="G72" s="46"/>
-      <c r="H72" s="67"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="56"/>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B73" s="21"/>
@@ -3110,7 +3110,7 @@
       <c r="H73" s="21"/>
     </row>
     <row r="74" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="74" t="s">
+      <c r="B74" s="42" t="s">
         <v>89</v>
       </c>
       <c r="C74" s="47" t="s">
@@ -3119,47 +3119,47 @@
       <c r="D74" s="13">
         <v>1</v>
       </c>
-      <c r="E74" s="14" t="s">
+      <c r="E74" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="F74" s="62" t="s">
+      <c r="F74" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="71" t="s">
+      <c r="G74" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H74" s="68" t="s">
+      <c r="H74" s="36" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B75" s="40"/>
+      <c r="B75" s="43"/>
       <c r="C75" s="47"/>
       <c r="D75" s="13">
         <v>2</v>
       </c>
-      <c r="E75" s="14" t="s">
+      <c r="E75" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="F75" s="75"/>
-      <c r="G75" s="72"/>
-      <c r="H75" s="69"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="37"/>
     </row>
     <row r="76" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B76" s="40"/>
+      <c r="B76" s="43"/>
       <c r="C76" s="47"/>
       <c r="D76" s="13">
         <v>3</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E76" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="F76" s="76"/>
-      <c r="G76" s="73"/>
-      <c r="H76" s="69"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="37"/>
     </row>
     <row r="77" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="40"/>
+      <c r="B77" s="43"/>
       <c r="C77" s="47" t="s">
         <v>91</v>
       </c>
@@ -3169,16 +3169,16 @@
       <c r="E77" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F77" s="62" t="s">
+      <c r="F77" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="71" t="s">
+      <c r="G77" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H77" s="69"/>
+      <c r="H77" s="37"/>
     </row>
     <row r="78" spans="2:14" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="40"/>
+      <c r="B78" s="43"/>
       <c r="C78" s="47"/>
       <c r="D78" s="13">
         <v>2</v>
@@ -3186,12 +3186,12 @@
       <c r="E78" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="F78" s="75"/>
-      <c r="G78" s="72"/>
-      <c r="H78" s="69"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="37"/>
     </row>
     <row r="79" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="40"/>
+      <c r="B79" s="43"/>
       <c r="C79" s="47"/>
       <c r="D79" s="13">
         <v>3</v>
@@ -3199,12 +3199,12 @@
       <c r="E79" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="F79" s="75"/>
-      <c r="G79" s="72"/>
-      <c r="H79" s="69"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="37"/>
     </row>
     <row r="80" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B80" s="40"/>
+      <c r="B80" s="43"/>
       <c r="C80" s="47"/>
       <c r="D80" s="13">
         <v>4</v>
@@ -3212,12 +3212,12 @@
       <c r="E80" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="F80" s="76"/>
-      <c r="G80" s="73"/>
-      <c r="H80" s="69"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="37"/>
     </row>
     <row r="81" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="40"/>
+      <c r="B81" s="43"/>
       <c r="C81" s="47" t="s">
         <v>92</v>
       </c>
@@ -3227,16 +3227,16 @@
       <c r="E81" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F81" s="62" t="s">
+      <c r="F81" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="71" t="s">
+      <c r="G81" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H81" s="69"/>
+      <c r="H81" s="37"/>
     </row>
     <row r="82" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="40"/>
+      <c r="B82" s="43"/>
       <c r="C82" s="47"/>
       <c r="D82" s="13">
         <v>2</v>
@@ -3244,12 +3244,12 @@
       <c r="E82" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="F82" s="75"/>
-      <c r="G82" s="72"/>
-      <c r="H82" s="69"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="37"/>
     </row>
     <row r="83" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B83" s="40"/>
+      <c r="B83" s="43"/>
       <c r="C83" s="47"/>
       <c r="D83" s="13">
         <v>3</v>
@@ -3257,12 +3257,12 @@
       <c r="E83" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="F83" s="75"/>
-      <c r="G83" s="72"/>
-      <c r="H83" s="69"/>
+      <c r="F83" s="45"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="37"/>
     </row>
     <row r="84" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B84" s="40"/>
+      <c r="B84" s="43"/>
       <c r="C84" s="47"/>
       <c r="D84" s="13">
         <v>4</v>
@@ -3270,9 +3270,9 @@
       <c r="E84" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F84" s="76"/>
-      <c r="G84" s="73"/>
-      <c r="H84" s="70"/>
+      <c r="F84" s="46"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="38"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="20"/>
@@ -3280,48 +3280,13 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="H74:H84"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="G77:G80"/>
-    <mergeCell ref="G81:G84"/>
-    <mergeCell ref="B74:B84"/>
-    <mergeCell ref="F81:F84"/>
-    <mergeCell ref="F77:F80"/>
-    <mergeCell ref="F74:F76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C81:C84"/>
-    <mergeCell ref="H46:H55"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="G57:G60"/>
-    <mergeCell ref="B57:B72"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="F61:F64"/>
-    <mergeCell ref="F57:F60"/>
-    <mergeCell ref="F65:F68"/>
-    <mergeCell ref="F69:F72"/>
-    <mergeCell ref="G61:G64"/>
-    <mergeCell ref="G65:G68"/>
-    <mergeCell ref="G69:G72"/>
-    <mergeCell ref="H57:H72"/>
-    <mergeCell ref="C61:C64"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="F51:F55"/>
-    <mergeCell ref="G51:G55"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="G46:G50"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="B26:B44"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H11:H24"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="G5:G9"/>
     <mergeCell ref="B11:B24"/>
     <mergeCell ref="H26:H44"/>
     <mergeCell ref="G26:G30"/>
@@ -3338,13 +3303,48 @@
     <mergeCell ref="C11:C15"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="G16:G20"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="F5:F9"/>
-    <mergeCell ref="G5:G9"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H11:H24"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="F46:F50"/>
+    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="B26:B44"/>
+    <mergeCell ref="H46:H55"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="B57:B72"/>
+    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="F65:F68"/>
+    <mergeCell ref="F69:F72"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="G65:G68"/>
+    <mergeCell ref="G69:G72"/>
+    <mergeCell ref="H57:H72"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="H74:H84"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="G77:G80"/>
+    <mergeCell ref="G81:G84"/>
+    <mergeCell ref="B74:B84"/>
+    <mergeCell ref="F81:F84"/>
+    <mergeCell ref="F77:F80"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="C81:C84"/>
   </mergeCells>
   <conditionalFormatting sqref="F5">
     <cfRule type="containsText" dxfId="53" priority="68" operator="containsText" text="MEDIUM">

--- a/Documentacion/Hsitorias_Usuario.xlsx
+++ b/Documentacion/Hsitorias_Usuario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50178dff44962c00/Escritorio/Software_Inventario/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{555E0851-B4CC-4AAA-8D83-19A708D5042A}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A66B990-3FB4-463C-ABC5-92A3459BEC59}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,6 +796,108 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -817,113 +919,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1691,13 +1691,13 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="16" t="s">
@@ -1706,10 +1706,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="77" t="s">
+      <c r="D4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="77"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="15" t="s">
         <v>2</v>
       </c>
@@ -1727,10 +1727,10 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="39" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="13">
@@ -1739,13 +1739,13 @@
       <c r="E5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="70" t="s">
+      <c r="G5" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="78" t="s">
+      <c r="H5" s="41" t="s">
         <v>105</v>
       </c>
       <c r="I5" s="1"/>
@@ -1756,17 +1756,17 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="70"/>
-      <c r="C6" s="72"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="40"/>
       <c r="D6" s="13">
         <v>2</v>
       </c>
       <c r="E6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="78"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="41"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1775,17 +1775,17 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="70"/>
-      <c r="C7" s="72"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="13">
         <v>3</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="78"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="41"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1794,17 +1794,17 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="70"/>
-      <c r="C8" s="72"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="40"/>
       <c r="D8" s="13">
         <v>4</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="78"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="41"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1813,17 +1813,17 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="70"/>
-      <c r="C9" s="72"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="40"/>
       <c r="D9" s="13">
         <v>5</v>
       </c>
       <c r="E9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="78"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="41"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1847,10 +1847,10 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="39" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="13">
@@ -1859,13 +1859,13 @@
       <c r="E11" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="70" t="s">
+      <c r="G11" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="56" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1"/>
@@ -1876,17 +1876,17 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="69"/>
-      <c r="C12" s="72"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="13">
         <v>2</v>
       </c>
       <c r="E12" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="67"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="57"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1895,17 +1895,17 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="69"/>
-      <c r="C13" s="72"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="40"/>
       <c r="D13" s="13">
         <v>3</v>
       </c>
       <c r="E13" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="67"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="57"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1914,17 +1914,17 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="69"/>
-      <c r="C14" s="72"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="40"/>
       <c r="D14" s="13">
         <v>4</v>
       </c>
       <c r="E14" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="67"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="57"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1933,17 +1933,17 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="69"/>
-      <c r="C15" s="72"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="40"/>
       <c r="D15" s="13">
         <v>5</v>
       </c>
       <c r="E15" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="67"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="57"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1952,8 +1952,8 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="69"/>
-      <c r="C16" s="71" t="s">
+      <c r="B16" s="43"/>
+      <c r="C16" s="39" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="13">
@@ -1962,13 +1962,13 @@
       <c r="E16" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="67"/>
+      <c r="H16" s="57"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1977,17 +1977,17 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="69"/>
-      <c r="C17" s="71"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="39"/>
       <c r="D17" s="13">
         <v>2</v>
       </c>
       <c r="E17" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="67"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="57"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1996,17 +1996,17 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="69"/>
-      <c r="C18" s="71"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="39"/>
       <c r="D18" s="13">
         <v>3</v>
       </c>
       <c r="E18" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="43"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="67"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="57"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -2015,17 +2015,17 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="69"/>
-      <c r="C19" s="71"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="39"/>
       <c r="D19" s="13">
         <v>4</v>
       </c>
       <c r="E19" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="67"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="57"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -2034,17 +2034,17 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="69"/>
-      <c r="C20" s="71"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="39"/>
       <c r="D20" s="13">
         <v>5</v>
       </c>
       <c r="E20" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="67"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="57"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -2053,8 +2053,8 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="69"/>
-      <c r="C21" s="47" t="s">
+      <c r="B21" s="43"/>
+      <c r="C21" s="49" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="13">
@@ -2063,13 +2063,13 @@
       <c r="E21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="43" t="s">
+      <c r="F21" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="63" t="s">
+      <c r="G21" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="67"/>
+      <c r="H21" s="57"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -2078,17 +2078,17 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="69"/>
-      <c r="C22" s="47"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="49"/>
       <c r="D22" s="13">
         <v>2</v>
       </c>
       <c r="E22" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="67"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="57"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2097,17 +2097,17 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="69"/>
-      <c r="C23" s="47"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="49"/>
       <c r="D23" s="13">
         <v>3</v>
       </c>
       <c r="E23" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="43"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="67"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="57"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2116,7 +2116,7 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="2:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="69"/>
+      <c r="B24" s="43"/>
       <c r="C24" s="12" t="s">
         <v>104</v>
       </c>
@@ -2132,7 +2132,7 @@
       <c r="G24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="68"/>
+      <c r="H24" s="58"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2156,10 +2156,10 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="49" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="13">
@@ -2168,13 +2168,13 @@
       <c r="E26" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="61" t="s">
+      <c r="G26" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="48" t="s">
+      <c r="H26" s="44" t="s">
         <v>58</v>
       </c>
       <c r="I26" s="1"/>
@@ -2185,17 +2185,17 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:14" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
-      <c r="C27" s="47"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="49"/>
       <c r="D27" s="13">
         <v>2</v>
       </c>
       <c r="E27" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="49"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="45"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2204,17 +2204,17 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
-      <c r="C28" s="47"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="49"/>
       <c r="D28" s="13">
         <v>3</v>
       </c>
       <c r="E28" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="43"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="49"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="45"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2223,30 +2223,30 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="2:14" s="4" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
-      <c r="C29" s="47"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="13">
         <v>4</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="43"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="49"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="47"/>
+      <c r="H29" s="45"/>
     </row>
     <row r="30" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="52"/>
-      <c r="C30" s="47"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="49"/>
       <c r="D30" s="13">
         <v>5</v>
       </c>
       <c r="E30" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="43"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="49"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="45"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2255,8 +2255,8 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="2:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="52"/>
-      <c r="C31" s="47" t="s">
+      <c r="B31" s="59"/>
+      <c r="C31" s="49" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="13">
@@ -2265,13 +2265,13 @@
       <c r="E31" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="43" t="s">
+      <c r="F31" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="51" t="s">
+      <c r="G31" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="49"/>
+      <c r="H31" s="45"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2280,17 +2280,17 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="52"/>
-      <c r="C32" s="47"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="49"/>
       <c r="D32" s="13">
         <v>2</v>
       </c>
       <c r="E32" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="43"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="49"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="45"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2299,17 +2299,17 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
-      <c r="C33" s="47"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="49"/>
       <c r="D33" s="13">
         <v>3</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="43"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="49"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="45"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2318,17 +2318,17 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
-      <c r="C34" s="47"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="49"/>
       <c r="D34" s="13">
         <v>4</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="43"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="49"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="45"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2337,8 +2337,8 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="52"/>
-      <c r="C35" s="47" t="s">
+      <c r="B35" s="59"/>
+      <c r="C35" s="49" t="s">
         <v>109</v>
       </c>
       <c r="D35" s="13">
@@ -2347,13 +2347,13 @@
       <c r="E35" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="43" t="s">
+      <c r="F35" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="51" t="s">
+      <c r="G35" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="49"/>
+      <c r="H35" s="45"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2362,17 +2362,17 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
-      <c r="C36" s="47"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="49"/>
       <c r="D36" s="13">
         <v>2</v>
       </c>
       <c r="E36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="43"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="49"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="45"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2381,17 +2381,17 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="52"/>
-      <c r="C37" s="47"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="49"/>
       <c r="D37" s="13">
         <v>3</v>
       </c>
-      <c r="E37" s="14" t="s">
+      <c r="E37" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="43"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="49"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="45"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2400,17 +2400,17 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="52"/>
-      <c r="C38" s="47"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="49"/>
       <c r="D38" s="13">
         <v>4</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="43"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="49"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="45"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2419,17 +2419,17 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="52"/>
-      <c r="C39" s="47"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="49"/>
       <c r="D39" s="13">
         <v>5</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="43"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="49"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="45"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2438,23 +2438,23 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="52"/>
-      <c r="C40" s="47" t="s">
+      <c r="B40" s="59"/>
+      <c r="C40" s="49" t="s">
         <v>40</v>
       </c>
       <c r="D40" s="13">
         <v>1</v>
       </c>
-      <c r="E40" s="14" t="s">
+      <c r="E40" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="43" t="s">
+      <c r="F40" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="51" t="s">
+      <c r="G40" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="49"/>
+      <c r="H40" s="45"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2463,17 +2463,17 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="52"/>
-      <c r="C41" s="47"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="49"/>
       <c r="D41" s="13">
         <v>2</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="43"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="49"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="45"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2482,17 +2482,17 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="52"/>
-      <c r="C42" s="47"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="49"/>
       <c r="D42" s="13">
         <v>3</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="43"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="49"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="45"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2501,17 +2501,17 @@
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="52"/>
-      <c r="C43" s="47"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="49"/>
       <c r="D43" s="13">
         <v>4</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F43" s="43"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="49"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="45"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2520,17 +2520,17 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="52"/>
-      <c r="C44" s="47"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="49"/>
       <c r="D44" s="13">
         <v>5</v>
       </c>
-      <c r="E44" s="14" t="s">
+      <c r="E44" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="43"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="50"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="46"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2554,10 +2554,10 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="52" t="s">
+      <c r="B46" s="59" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="63" t="s">
         <v>60</v>
       </c>
       <c r="D46" s="13">
@@ -2566,13 +2566,13 @@
       <c r="E46" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="43" t="s">
+      <c r="F46" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="61" t="s">
+      <c r="G46" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="48" t="s">
+      <c r="H46" s="44" t="s">
         <v>70</v>
       </c>
       <c r="I46" s="1"/>
@@ -2583,17 +2583,17 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B47" s="52"/>
-      <c r="C47" s="60"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="63"/>
       <c r="D47" s="13">
         <v>2</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F47" s="43"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="49"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="45"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2602,17 +2602,17 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B48" s="52"/>
-      <c r="C48" s="60"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="63"/>
       <c r="D48" s="13">
         <v>3</v>
       </c>
       <c r="E48" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="43"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="49"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="47"/>
+      <c r="H48" s="45"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2621,17 +2621,17 @@
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B49" s="52"/>
-      <c r="C49" s="60"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="63"/>
       <c r="D49" s="13">
         <v>4</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="43"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="49"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="45"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2640,17 +2640,17 @@
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B50" s="52"/>
-      <c r="C50" s="60"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="63"/>
       <c r="D50" s="13">
         <v>5</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="44"/>
-      <c r="G50" s="62"/>
-      <c r="H50" s="49"/>
+      <c r="F50" s="64"/>
+      <c r="G50" s="65"/>
+      <c r="H50" s="45"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2659,8 +2659,8 @@
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="52"/>
-      <c r="C51" s="47" t="s">
+      <c r="B51" s="59"/>
+      <c r="C51" s="49" t="s">
         <v>61</v>
       </c>
       <c r="D51" s="19">
@@ -2669,13 +2669,13 @@
       <c r="E51" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F51" s="43" t="s">
+      <c r="F51" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="57" t="s">
+      <c r="G51" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="49"/>
+      <c r="H51" s="45"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2684,17 +2684,17 @@
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B52" s="52"/>
-      <c r="C52" s="47"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="49"/>
       <c r="D52" s="19">
         <v>2</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="43"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="49"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="61"/>
+      <c r="H52" s="45"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2703,17 +2703,17 @@
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B53" s="52"/>
-      <c r="C53" s="47"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="49"/>
       <c r="D53" s="19">
         <v>3</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="43"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="49"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="61"/>
+      <c r="H53" s="45"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2722,17 +2722,17 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B54" s="52"/>
-      <c r="C54" s="47"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="49"/>
       <c r="D54" s="13">
         <v>4</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="43"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="49"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="61"/>
+      <c r="H54" s="45"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -2741,17 +2741,17 @@
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="52"/>
-      <c r="C55" s="47"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="49"/>
       <c r="D55" s="13">
         <v>5</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F55" s="43"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="50"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="62"/>
+      <c r="H55" s="46"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2775,10 +2775,10 @@
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="2:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="52" t="s">
+      <c r="B57" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="49" t="s">
         <v>72</v>
       </c>
       <c r="D57" s="13">
@@ -2787,13 +2787,13 @@
       <c r="E57" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="F57" s="53" t="s">
+      <c r="F57" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="51" t="s">
+      <c r="G57" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="H57" s="56" t="s">
+      <c r="H57" s="69" t="s">
         <v>88</v>
       </c>
       <c r="I57" s="1"/>
@@ -2804,17 +2804,17 @@
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="52"/>
-      <c r="C58" s="47"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="49"/>
       <c r="D58" s="13">
         <v>2</v>
       </c>
       <c r="E58" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="54"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="56"/>
+      <c r="F58" s="67"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="69"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2823,17 +2823,17 @@
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="52"/>
-      <c r="C59" s="47"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="49"/>
       <c r="D59" s="13">
         <v>3</v>
       </c>
       <c r="E59" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="F59" s="54"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="56"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="69"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2842,17 +2842,17 @@
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="2:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="52"/>
-      <c r="C60" s="47"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="49"/>
       <c r="D60" s="13">
         <v>4</v>
       </c>
       <c r="E60" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="F60" s="55"/>
-      <c r="G60" s="51"/>
-      <c r="H60" s="56"/>
+      <c r="F60" s="68"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="69"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2861,8 +2861,8 @@
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="52"/>
-      <c r="C61" s="47" t="s">
+      <c r="B61" s="59"/>
+      <c r="C61" s="49" t="s">
         <v>73</v>
       </c>
       <c r="D61" s="13">
@@ -2871,13 +2871,13 @@
       <c r="E61" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="F61" s="53" t="s">
+      <c r="F61" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="51" t="s">
+      <c r="G61" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H61" s="56"/>
+      <c r="H61" s="69"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2886,17 +2886,17 @@
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="52"/>
-      <c r="C62" s="47"/>
+      <c r="B62" s="59"/>
+      <c r="C62" s="49"/>
       <c r="D62" s="13">
         <v>2</v>
       </c>
       <c r="E62" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F62" s="54"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="56"/>
+      <c r="F62" s="67"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="69"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -2905,17 +2905,17 @@
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="2:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="52"/>
-      <c r="C63" s="47"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="49"/>
       <c r="D63" s="13">
         <v>3</v>
       </c>
       <c r="E63" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="F63" s="54"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="56"/>
+      <c r="F63" s="67"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="69"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -2924,17 +2924,17 @@
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="2:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="52"/>
-      <c r="C64" s="47"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="49"/>
       <c r="D64" s="13">
         <v>4</v>
       </c>
       <c r="E64" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="55"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="56"/>
+      <c r="F64" s="68"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="69"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -2943,8 +2943,8 @@
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="52"/>
-      <c r="C65" s="47" t="s">
+      <c r="B65" s="59"/>
+      <c r="C65" s="49" t="s">
         <v>75</v>
       </c>
       <c r="D65" s="13">
@@ -2953,13 +2953,13 @@
       <c r="E65" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="F65" s="53" t="s">
+      <c r="F65" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="51" t="s">
+      <c r="G65" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="56"/>
+      <c r="H65" s="69"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2968,17 +2968,17 @@
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B66" s="52"/>
-      <c r="C66" s="47"/>
+      <c r="B66" s="59"/>
+      <c r="C66" s="49"/>
       <c r="D66" s="13">
         <v>2</v>
       </c>
       <c r="E66" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="54"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="56"/>
+      <c r="F66" s="67"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="69"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2987,17 +2987,17 @@
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B67" s="52"/>
-      <c r="C67" s="47"/>
+      <c r="B67" s="59"/>
+      <c r="C67" s="49"/>
       <c r="D67" s="13">
         <v>3</v>
       </c>
       <c r="E67" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="F67" s="54"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="56"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="48"/>
+      <c r="H67" s="69"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -3006,17 +3006,17 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="52"/>
-      <c r="C68" s="47"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="49"/>
       <c r="D68" s="13">
         <v>4</v>
       </c>
       <c r="E68" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F68" s="55"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="56"/>
+      <c r="F68" s="68"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="69"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -3025,8 +3025,8 @@
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="2:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="52"/>
-      <c r="C69" s="47" t="s">
+      <c r="B69" s="59"/>
+      <c r="C69" s="49" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="13">
@@ -3035,13 +3035,13 @@
       <c r="E69" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="F69" s="43" t="s">
+      <c r="F69" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G69" s="51" t="s">
+      <c r="G69" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="H69" s="56"/>
+      <c r="H69" s="69"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3050,17 +3050,17 @@
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B70" s="52"/>
-      <c r="C70" s="47"/>
+      <c r="B70" s="59"/>
+      <c r="C70" s="49"/>
       <c r="D70" s="13">
         <v>2</v>
       </c>
       <c r="E70" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="F70" s="43"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="56"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="69"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3069,17 +3069,17 @@
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B71" s="52"/>
-      <c r="C71" s="47"/>
+      <c r="B71" s="59"/>
+      <c r="C71" s="49"/>
       <c r="D71" s="13">
         <v>3</v>
       </c>
       <c r="E71" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="F71" s="43"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="56"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="69"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3088,17 +3088,17 @@
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="52"/>
-      <c r="C72" s="47"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="49"/>
       <c r="D72" s="13">
         <v>4</v>
       </c>
       <c r="E72" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F72" s="43"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="56"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="69"/>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B73" s="21"/>
@@ -3110,10 +3110,10 @@
       <c r="H73" s="21"/>
     </row>
     <row r="74" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="42" t="s">
+      <c r="B74" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="C74" s="47" t="s">
+      <c r="C74" s="49" t="s">
         <v>90</v>
       </c>
       <c r="D74" s="13">
@@ -3122,157 +3122,157 @@
       <c r="E74" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="F74" s="44" t="s">
+      <c r="F74" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="39" t="s">
+      <c r="G74" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H74" s="36" t="s">
+      <c r="H74" s="70" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B75" s="43"/>
-      <c r="C75" s="47"/>
+      <c r="B75" s="42"/>
+      <c r="C75" s="49"/>
       <c r="D75" s="13">
         <v>2</v>
       </c>
       <c r="E75" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="F75" s="45"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="37"/>
+      <c r="F75" s="77"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="71"/>
     </row>
     <row r="76" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B76" s="43"/>
-      <c r="C76" s="47"/>
+      <c r="B76" s="42"/>
+      <c r="C76" s="49"/>
       <c r="D76" s="13">
         <v>3</v>
       </c>
       <c r="E76" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="F76" s="46"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="37"/>
+      <c r="F76" s="78"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="71"/>
     </row>
     <row r="77" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="43"/>
-      <c r="C77" s="47" t="s">
+      <c r="B77" s="42"/>
+      <c r="C77" s="49" t="s">
         <v>91</v>
       </c>
       <c r="D77" s="13">
         <v>1</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="F77" s="44" t="s">
+      <c r="F77" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="39" t="s">
+      <c r="G77" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H77" s="37"/>
+      <c r="H77" s="71"/>
     </row>
     <row r="78" spans="2:14" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="43"/>
-      <c r="C78" s="47"/>
+      <c r="B78" s="42"/>
+      <c r="C78" s="49"/>
       <c r="D78" s="13">
         <v>2</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F78" s="45"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="37"/>
+      <c r="F78" s="77"/>
+      <c r="G78" s="74"/>
+      <c r="H78" s="71"/>
     </row>
     <row r="79" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="43"/>
-      <c r="C79" s="47"/>
+      <c r="B79" s="42"/>
+      <c r="C79" s="49"/>
       <c r="D79" s="13">
         <v>3</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="F79" s="45"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="37"/>
+      <c r="F79" s="77"/>
+      <c r="G79" s="74"/>
+      <c r="H79" s="71"/>
     </row>
     <row r="80" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B80" s="43"/>
-      <c r="C80" s="47"/>
+      <c r="B80" s="42"/>
+      <c r="C80" s="49"/>
       <c r="D80" s="13">
         <v>4</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="F80" s="46"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="37"/>
+      <c r="F80" s="78"/>
+      <c r="G80" s="75"/>
+      <c r="H80" s="71"/>
     </row>
     <row r="81" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="43"/>
-      <c r="C81" s="47" t="s">
+      <c r="B81" s="42"/>
+      <c r="C81" s="49" t="s">
         <v>92</v>
       </c>
       <c r="D81" s="13">
         <v>1</v>
       </c>
-      <c r="E81" s="14" t="s">
+      <c r="E81" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="F81" s="44" t="s">
+      <c r="F81" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="39" t="s">
+      <c r="G81" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H81" s="37"/>
+      <c r="H81" s="71"/>
     </row>
     <row r="82" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="43"/>
-      <c r="C82" s="47"/>
+      <c r="B82" s="42"/>
+      <c r="C82" s="49"/>
       <c r="D82" s="13">
         <v>2</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E82" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F82" s="45"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="37"/>
+      <c r="F82" s="77"/>
+      <c r="G82" s="74"/>
+      <c r="H82" s="71"/>
     </row>
     <row r="83" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B83" s="43"/>
-      <c r="C83" s="47"/>
+      <c r="B83" s="42"/>
+      <c r="C83" s="49"/>
       <c r="D83" s="13">
         <v>3</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E83" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="F83" s="45"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="37"/>
+      <c r="F83" s="77"/>
+      <c r="G83" s="74"/>
+      <c r="H83" s="71"/>
     </row>
     <row r="84" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B84" s="43"/>
-      <c r="C84" s="47"/>
+      <c r="B84" s="42"/>
+      <c r="C84" s="49"/>
       <c r="D84" s="13">
         <v>4</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E84" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F84" s="46"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="38"/>
+      <c r="F84" s="78"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="72"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="20"/>
@@ -3280,13 +3280,48 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="F5:F9"/>
-    <mergeCell ref="G5:G9"/>
+    <mergeCell ref="H74:H84"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="G77:G80"/>
+    <mergeCell ref="G81:G84"/>
+    <mergeCell ref="B74:B84"/>
+    <mergeCell ref="F81:F84"/>
+    <mergeCell ref="F77:F80"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="H46:H55"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="B57:B72"/>
+    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="F65:F68"/>
+    <mergeCell ref="F69:F72"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="G65:G68"/>
+    <mergeCell ref="G69:G72"/>
+    <mergeCell ref="H57:H72"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="F46:F50"/>
+    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="B26:B44"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H11:H24"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C35:C39"/>
     <mergeCell ref="B11:B24"/>
     <mergeCell ref="H26:H44"/>
     <mergeCell ref="G26:G30"/>
@@ -3303,48 +3338,13 @@
     <mergeCell ref="C11:C15"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H11:H24"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="F51:F55"/>
-    <mergeCell ref="G51:G55"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="G46:G50"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="B26:B44"/>
-    <mergeCell ref="H46:H55"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="G57:G60"/>
-    <mergeCell ref="B57:B72"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="F61:F64"/>
-    <mergeCell ref="F57:F60"/>
-    <mergeCell ref="F65:F68"/>
-    <mergeCell ref="F69:F72"/>
-    <mergeCell ref="G61:G64"/>
-    <mergeCell ref="G65:G68"/>
-    <mergeCell ref="G69:G72"/>
-    <mergeCell ref="H57:H72"/>
-    <mergeCell ref="C61:C64"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="H74:H84"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="G77:G80"/>
-    <mergeCell ref="G81:G84"/>
-    <mergeCell ref="B74:B84"/>
-    <mergeCell ref="F81:F84"/>
-    <mergeCell ref="F77:F80"/>
-    <mergeCell ref="F74:F76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="G5:G9"/>
   </mergeCells>
   <conditionalFormatting sqref="F5">
     <cfRule type="containsText" dxfId="53" priority="68" operator="containsText" text="MEDIUM">

--- a/Documentacion/Hsitorias_Usuario.xlsx
+++ b/Documentacion/Hsitorias_Usuario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50178dff44962c00/Escritorio/Software_Inventario/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A66B990-3FB4-463C-ABC5-92A3459BEC59}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1E001CD-8304-4A40-8CD4-4E04C7C10C38}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -796,134 +796,134 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1691,13 +1691,13 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="76"/>
+      <c r="G3" s="76"/>
+      <c r="H3" s="76"/>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="16" t="s">
@@ -1706,10 +1706,10 @@
       <c r="C4" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="37" t="s">
+      <c r="D4" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="37"/>
+      <c r="E4" s="77"/>
       <c r="F4" s="15" t="s">
         <v>2</v>
       </c>
@@ -1727,10 +1727,10 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="71" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="13">
@@ -1739,13 +1739,13 @@
       <c r="E5" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="38" t="s">
+      <c r="G5" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="78" t="s">
         <v>105</v>
       </c>
       <c r="I5" s="1"/>
@@ -1756,17 +1756,17 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="38"/>
-      <c r="C6" s="40"/>
+      <c r="B6" s="70"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="13">
         <v>2</v>
       </c>
       <c r="E6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="38"/>
-      <c r="H6" s="41"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="78"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1775,17 +1775,17 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="38"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="13">
         <v>3</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="41"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="78"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1794,17 +1794,17 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="38"/>
-      <c r="C8" s="40"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="13">
         <v>4</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="41"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="78"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1813,17 +1813,17 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="38"/>
-      <c r="C9" s="40"/>
+      <c r="B9" s="70"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="13">
         <v>5</v>
       </c>
       <c r="E9" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="41"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="78"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1847,10 +1847,10 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="71" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="13">
@@ -1859,13 +1859,13 @@
       <c r="E11" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="38" t="s">
+      <c r="G11" s="70" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="56" t="s">
+      <c r="H11" s="66" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1"/>
@@ -1876,17 +1876,17 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="43"/>
-      <c r="C12" s="40"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="72"/>
       <c r="D12" s="13">
         <v>2</v>
       </c>
       <c r="E12" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="57"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="67"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1895,17 +1895,17 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="43"/>
-      <c r="C13" s="40"/>
+      <c r="B13" s="69"/>
+      <c r="C13" s="72"/>
       <c r="D13" s="13">
         <v>3</v>
       </c>
       <c r="E13" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="57"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="67"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1914,17 +1914,17 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="43"/>
-      <c r="C14" s="40"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="72"/>
       <c r="D14" s="13">
         <v>4</v>
       </c>
       <c r="E14" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="57"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="67"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1933,17 +1933,17 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="43"/>
-      <c r="C15" s="40"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="72"/>
       <c r="D15" s="13">
         <v>5</v>
       </c>
       <c r="E15" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="57"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="67"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1952,8 +1952,8 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="43"/>
-      <c r="C16" s="39" t="s">
+      <c r="B16" s="69"/>
+      <c r="C16" s="71" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="13">
@@ -1962,13 +1962,13 @@
       <c r="E16" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="50" t="s">
+      <c r="G16" s="73" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="57"/>
+      <c r="H16" s="67"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1977,17 +1977,17 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="43"/>
-      <c r="C17" s="39"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="71"/>
       <c r="D17" s="13">
         <v>2</v>
       </c>
       <c r="E17" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="57"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="67"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1996,17 +1996,17 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="43"/>
-      <c r="C18" s="39"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="71"/>
       <c r="D18" s="13">
         <v>3</v>
       </c>
       <c r="E18" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="57"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="67"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -2015,17 +2015,17 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="43"/>
-      <c r="C19" s="39"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="71"/>
       <c r="D19" s="13">
         <v>4</v>
       </c>
       <c r="E19" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="57"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="67"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -2034,17 +2034,17 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="43"/>
-      <c r="C20" s="39"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="71"/>
       <c r="D20" s="13">
         <v>5</v>
       </c>
       <c r="E20" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="42"/>
-      <c r="G20" s="52"/>
-      <c r="H20" s="57"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="75"/>
+      <c r="H20" s="67"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -2053,8 +2053,8 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="43"/>
-      <c r="C21" s="49" t="s">
+      <c r="B21" s="69"/>
+      <c r="C21" s="47" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="13">
@@ -2063,13 +2063,13 @@
       <c r="E21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="53" t="s">
+      <c r="G21" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="57"/>
+      <c r="H21" s="67"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -2078,17 +2078,17 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="43"/>
-      <c r="C22" s="49"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="47"/>
       <c r="D22" s="13">
         <v>2</v>
       </c>
       <c r="E22" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="42"/>
-      <c r="G22" s="54"/>
-      <c r="H22" s="57"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="67"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2097,17 +2097,17 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="43"/>
-      <c r="C23" s="49"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="47"/>
       <c r="D23" s="13">
         <v>3</v>
       </c>
       <c r="E23" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="42"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="57"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="67"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2116,7 +2116,7 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="2:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="43"/>
+      <c r="B24" s="69"/>
       <c r="C24" s="12" t="s">
         <v>104</v>
       </c>
@@ -2132,7 +2132,7 @@
       <c r="G24" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="58"/>
+      <c r="H24" s="68"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2156,10 +2156,10 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="47" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="13">
@@ -2168,13 +2168,13 @@
       <c r="E26" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="42" t="s">
+      <c r="F26" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="47" t="s">
+      <c r="G26" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="48" t="s">
         <v>58</v>
       </c>
       <c r="I26" s="1"/>
@@ -2185,17 +2185,17 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:14" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="59"/>
-      <c r="C27" s="49"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="47"/>
       <c r="D27" s="13">
         <v>2</v>
       </c>
       <c r="E27" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="42"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="45"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="49"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2204,17 +2204,17 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="59"/>
-      <c r="C28" s="49"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="47"/>
       <c r="D28" s="13">
         <v>3</v>
       </c>
       <c r="E28" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="42"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="45"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="49"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2223,30 +2223,30 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="2:14" s="4" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="59"/>
-      <c r="C29" s="49"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="47"/>
       <c r="D29" s="13">
         <v>4</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="42"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="45"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="49"/>
     </row>
     <row r="30" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="59"/>
-      <c r="C30" s="49"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="47"/>
       <c r="D30" s="13">
         <v>5</v>
       </c>
       <c r="E30" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="42"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="45"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="49"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2255,8 +2255,8 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="2:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="59"/>
-      <c r="C31" s="49" t="s">
+      <c r="B31" s="52"/>
+      <c r="C31" s="47" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="13">
@@ -2265,13 +2265,13 @@
       <c r="E31" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="42" t="s">
+      <c r="F31" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="48" t="s">
+      <c r="G31" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="45"/>
+      <c r="H31" s="49"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2280,17 +2280,17 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="59"/>
-      <c r="C32" s="49"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="47"/>
       <c r="D32" s="13">
         <v>2</v>
       </c>
       <c r="E32" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="42"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="45"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="49"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2299,17 +2299,17 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="59"/>
-      <c r="C33" s="49"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="47"/>
       <c r="D33" s="13">
         <v>3</v>
       </c>
       <c r="E33" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="42"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="45"/>
+      <c r="F33" s="43"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="49"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2318,17 +2318,17 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="59"/>
-      <c r="C34" s="49"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="47"/>
       <c r="D34" s="13">
         <v>4</v>
       </c>
       <c r="E34" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="42"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="45"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="51"/>
+      <c r="H34" s="49"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2337,8 +2337,8 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="59"/>
-      <c r="C35" s="49" t="s">
+      <c r="B35" s="52"/>
+      <c r="C35" s="47" t="s">
         <v>109</v>
       </c>
       <c r="D35" s="13">
@@ -2347,13 +2347,13 @@
       <c r="E35" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="42" t="s">
+      <c r="F35" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="48" t="s">
+      <c r="G35" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="45"/>
+      <c r="H35" s="49"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2362,17 +2362,17 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="59"/>
-      <c r="C36" s="49"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="47"/>
       <c r="D36" s="13">
         <v>2</v>
       </c>
       <c r="E36" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="42"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="45"/>
+      <c r="F36" s="43"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="49"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2381,17 +2381,17 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="59"/>
-      <c r="C37" s="49"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="47"/>
       <c r="D37" s="13">
         <v>3</v>
       </c>
       <c r="E37" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="42"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="45"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="49"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2400,17 +2400,17 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="59"/>
-      <c r="C38" s="49"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="47"/>
       <c r="D38" s="13">
         <v>4</v>
       </c>
       <c r="E38" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="42"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="45"/>
+      <c r="F38" s="43"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="49"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2419,17 +2419,17 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="59"/>
-      <c r="C39" s="49"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="47"/>
       <c r="D39" s="13">
         <v>5</v>
       </c>
       <c r="E39" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="42"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="45"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="51"/>
+      <c r="H39" s="49"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2438,8 +2438,8 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="59"/>
-      <c r="C40" s="49" t="s">
+      <c r="B40" s="52"/>
+      <c r="C40" s="47" t="s">
         <v>40</v>
       </c>
       <c r="D40" s="13">
@@ -2448,13 +2448,13 @@
       <c r="E40" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="42" t="s">
+      <c r="F40" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="48" t="s">
+      <c r="G40" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="45"/>
+      <c r="H40" s="49"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2463,17 +2463,17 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="59"/>
-      <c r="C41" s="49"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="47"/>
       <c r="D41" s="13">
         <v>2</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="42"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="45"/>
+      <c r="F41" s="43"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="49"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2482,17 +2482,17 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="59"/>
-      <c r="C42" s="49"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="47"/>
       <c r="D42" s="13">
         <v>3</v>
       </c>
       <c r="E42" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="42"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="45"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="49"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2501,17 +2501,17 @@
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="59"/>
-      <c r="C43" s="49"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="47"/>
       <c r="D43" s="13">
         <v>4</v>
       </c>
       <c r="E43" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F43" s="42"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="45"/>
+      <c r="F43" s="43"/>
+      <c r="G43" s="51"/>
+      <c r="H43" s="49"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2520,17 +2520,17 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="59"/>
-      <c r="C44" s="49"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="47"/>
       <c r="D44" s="13">
         <v>5</v>
       </c>
       <c r="E44" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="42"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="46"/>
+      <c r="F44" s="43"/>
+      <c r="G44" s="51"/>
+      <c r="H44" s="50"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2554,25 +2554,25 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="52" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="63" t="s">
+      <c r="C46" s="60" t="s">
         <v>60</v>
       </c>
       <c r="D46" s="13">
         <v>1</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="42" t="s">
+      <c r="F46" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="47" t="s">
+      <c r="G46" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="44" t="s">
+      <c r="H46" s="48" t="s">
         <v>70</v>
       </c>
       <c r="I46" s="1"/>
@@ -2583,17 +2583,17 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B47" s="59"/>
-      <c r="C47" s="63"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="60"/>
       <c r="D47" s="13">
         <v>2</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F47" s="42"/>
-      <c r="G47" s="47"/>
-      <c r="H47" s="45"/>
+      <c r="F47" s="43"/>
+      <c r="G47" s="61"/>
+      <c r="H47" s="49"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2602,17 +2602,17 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B48" s="59"/>
-      <c r="C48" s="63"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="60"/>
       <c r="D48" s="13">
         <v>3</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="42"/>
-      <c r="G48" s="47"/>
-      <c r="H48" s="45"/>
+      <c r="F48" s="43"/>
+      <c r="G48" s="61"/>
+      <c r="H48" s="49"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2621,17 +2621,17 @@
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B49" s="59"/>
-      <c r="C49" s="63"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="60"/>
       <c r="D49" s="13">
         <v>4</v>
       </c>
-      <c r="E49" s="14" t="s">
+      <c r="E49" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="42"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="45"/>
+      <c r="F49" s="43"/>
+      <c r="G49" s="61"/>
+      <c r="H49" s="49"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2640,17 +2640,17 @@
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B50" s="59"/>
-      <c r="C50" s="63"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="60"/>
       <c r="D50" s="13">
         <v>5</v>
       </c>
-      <c r="E50" s="14" t="s">
+      <c r="E50" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="64"/>
-      <c r="G50" s="65"/>
-      <c r="H50" s="45"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="49"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2659,8 +2659,8 @@
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="59"/>
-      <c r="C51" s="49" t="s">
+      <c r="B51" s="52"/>
+      <c r="C51" s="47" t="s">
         <v>61</v>
       </c>
       <c r="D51" s="19">
@@ -2669,13 +2669,13 @@
       <c r="E51" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F51" s="42" t="s">
+      <c r="F51" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="60" t="s">
+      <c r="G51" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="45"/>
+      <c r="H51" s="49"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2684,17 +2684,17 @@
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B52" s="59"/>
-      <c r="C52" s="49"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="47"/>
       <c r="D52" s="19">
         <v>2</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="42"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="45"/>
+      <c r="F52" s="43"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="49"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2703,17 +2703,17 @@
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B53" s="59"/>
-      <c r="C53" s="49"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="47"/>
       <c r="D53" s="19">
         <v>3</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="42"/>
-      <c r="G53" s="61"/>
-      <c r="H53" s="45"/>
+      <c r="F53" s="43"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="49"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2722,17 +2722,17 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B54" s="59"/>
-      <c r="C54" s="49"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="47"/>
       <c r="D54" s="13">
         <v>4</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="42"/>
-      <c r="G54" s="61"/>
-      <c r="H54" s="45"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="49"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -2741,17 +2741,17 @@
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="59"/>
-      <c r="C55" s="49"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="47"/>
       <c r="D55" s="13">
         <v>5</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F55" s="42"/>
-      <c r="G55" s="62"/>
-      <c r="H55" s="46"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="50"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2775,10 +2775,10 @@
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="2:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="59" t="s">
+      <c r="B57" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="C57" s="49" t="s">
+      <c r="C57" s="47" t="s">
         <v>72</v>
       </c>
       <c r="D57" s="13">
@@ -2787,13 +2787,13 @@
       <c r="E57" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="F57" s="66" t="s">
+      <c r="F57" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="48" t="s">
+      <c r="G57" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="H57" s="69" t="s">
+      <c r="H57" s="56" t="s">
         <v>88</v>
       </c>
       <c r="I57" s="1"/>
@@ -2804,17 +2804,17 @@
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="59"/>
-      <c r="C58" s="49"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="47"/>
       <c r="D58" s="13">
         <v>2</v>
       </c>
       <c r="E58" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="67"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="69"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="51"/>
+      <c r="H58" s="56"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2823,17 +2823,17 @@
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="59"/>
-      <c r="C59" s="49"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="47"/>
       <c r="D59" s="13">
         <v>3</v>
       </c>
       <c r="E59" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="F59" s="67"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="69"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="51"/>
+      <c r="H59" s="56"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2842,17 +2842,17 @@
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="2:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="59"/>
-      <c r="C60" s="49"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="47"/>
       <c r="D60" s="13">
         <v>4</v>
       </c>
       <c r="E60" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="F60" s="68"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="69"/>
+      <c r="F60" s="55"/>
+      <c r="G60" s="51"/>
+      <c r="H60" s="56"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2861,8 +2861,8 @@
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="59"/>
-      <c r="C61" s="49" t="s">
+      <c r="B61" s="52"/>
+      <c r="C61" s="47" t="s">
         <v>73</v>
       </c>
       <c r="D61" s="13">
@@ -2871,13 +2871,13 @@
       <c r="E61" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="F61" s="66" t="s">
+      <c r="F61" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="48" t="s">
+      <c r="G61" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H61" s="69"/>
+      <c r="H61" s="56"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2886,17 +2886,17 @@
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="59"/>
-      <c r="C62" s="49"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="47"/>
       <c r="D62" s="13">
         <v>2</v>
       </c>
       <c r="E62" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F62" s="67"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="69"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="51"/>
+      <c r="H62" s="56"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -2905,17 +2905,17 @@
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="2:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="59"/>
-      <c r="C63" s="49"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="47"/>
       <c r="D63" s="13">
         <v>3</v>
       </c>
       <c r="E63" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="F63" s="67"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="69"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="51"/>
+      <c r="H63" s="56"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -2924,17 +2924,17 @@
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="2:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="59"/>
-      <c r="C64" s="49"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="47"/>
       <c r="D64" s="13">
         <v>4</v>
       </c>
       <c r="E64" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="68"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="69"/>
+      <c r="F64" s="55"/>
+      <c r="G64" s="51"/>
+      <c r="H64" s="56"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -2943,8 +2943,8 @@
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="59"/>
-      <c r="C65" s="49" t="s">
+      <c r="B65" s="52"/>
+      <c r="C65" s="47" t="s">
         <v>75</v>
       </c>
       <c r="D65" s="13">
@@ -2953,13 +2953,13 @@
       <c r="E65" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="F65" s="66" t="s">
+      <c r="F65" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="48" t="s">
+      <c r="G65" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="69"/>
+      <c r="H65" s="56"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2968,17 +2968,17 @@
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B66" s="59"/>
-      <c r="C66" s="49"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="47"/>
       <c r="D66" s="13">
         <v>2</v>
       </c>
       <c r="E66" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="67"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="69"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="51"/>
+      <c r="H66" s="56"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2987,17 +2987,17 @@
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B67" s="59"/>
-      <c r="C67" s="49"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="47"/>
       <c r="D67" s="13">
         <v>3</v>
       </c>
       <c r="E67" s="34" t="s">
         <v>83</v>
       </c>
-      <c r="F67" s="67"/>
-      <c r="G67" s="48"/>
-      <c r="H67" s="69"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="51"/>
+      <c r="H67" s="56"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -3006,17 +3006,17 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="59"/>
-      <c r="C68" s="49"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="47"/>
       <c r="D68" s="13">
         <v>4</v>
       </c>
       <c r="E68" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F68" s="68"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="69"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="51"/>
+      <c r="H68" s="56"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -3025,8 +3025,8 @@
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="2:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="59"/>
-      <c r="C69" s="49" t="s">
+      <c r="B69" s="52"/>
+      <c r="C69" s="47" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="13">
@@ -3035,13 +3035,13 @@
       <c r="E69" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="F69" s="42" t="s">
+      <c r="F69" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="G69" s="48" t="s">
+      <c r="G69" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="H69" s="69"/>
+      <c r="H69" s="56"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3050,17 +3050,17 @@
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B70" s="59"/>
-      <c r="C70" s="49"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="47"/>
       <c r="D70" s="13">
         <v>2</v>
       </c>
       <c r="E70" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="F70" s="42"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="69"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="51"/>
+      <c r="H70" s="56"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3069,17 +3069,17 @@
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B71" s="59"/>
-      <c r="C71" s="49"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="47"/>
       <c r="D71" s="13">
         <v>3</v>
       </c>
       <c r="E71" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="F71" s="42"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="69"/>
+      <c r="F71" s="43"/>
+      <c r="G71" s="51"/>
+      <c r="H71" s="56"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3088,17 +3088,17 @@
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="59"/>
-      <c r="C72" s="49"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="47"/>
       <c r="D72" s="13">
         <v>4</v>
       </c>
       <c r="E72" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="F72" s="42"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="69"/>
+      <c r="F72" s="43"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="56"/>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B73" s="21"/>
@@ -3110,10 +3110,10 @@
       <c r="H73" s="21"/>
     </row>
     <row r="74" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="76" t="s">
+      <c r="B74" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="C74" s="49" t="s">
+      <c r="C74" s="47" t="s">
         <v>90</v>
       </c>
       <c r="D74" s="13">
@@ -3122,45 +3122,45 @@
       <c r="E74" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="F74" s="64" t="s">
+      <c r="F74" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="73" t="s">
+      <c r="G74" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H74" s="70" t="s">
+      <c r="H74" s="36" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B75" s="42"/>
-      <c r="C75" s="49"/>
+      <c r="B75" s="43"/>
+      <c r="C75" s="47"/>
       <c r="D75" s="13">
         <v>2</v>
       </c>
       <c r="E75" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="F75" s="77"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="71"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="40"/>
+      <c r="H75" s="37"/>
     </row>
     <row r="76" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B76" s="42"/>
-      <c r="C76" s="49"/>
+      <c r="B76" s="43"/>
+      <c r="C76" s="47"/>
       <c r="D76" s="13">
         <v>3</v>
       </c>
       <c r="E76" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="F76" s="78"/>
-      <c r="G76" s="75"/>
-      <c r="H76" s="71"/>
+      <c r="F76" s="46"/>
+      <c r="G76" s="41"/>
+      <c r="H76" s="37"/>
     </row>
     <row r="77" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="42"/>
-      <c r="C77" s="49" t="s">
+      <c r="B77" s="43"/>
+      <c r="C77" s="47" t="s">
         <v>91</v>
       </c>
       <c r="D77" s="13">
@@ -3169,56 +3169,56 @@
       <c r="E77" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="F77" s="64" t="s">
+      <c r="F77" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="73" t="s">
+      <c r="G77" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H77" s="71"/>
+      <c r="H77" s="37"/>
     </row>
     <row r="78" spans="2:14" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="42"/>
-      <c r="C78" s="49"/>
+      <c r="B78" s="43"/>
+      <c r="C78" s="47"/>
       <c r="D78" s="13">
         <v>2</v>
       </c>
       <c r="E78" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="F78" s="77"/>
-      <c r="G78" s="74"/>
-      <c r="H78" s="71"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="40"/>
+      <c r="H78" s="37"/>
     </row>
     <row r="79" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="42"/>
-      <c r="C79" s="49"/>
+      <c r="B79" s="43"/>
+      <c r="C79" s="47"/>
       <c r="D79" s="13">
         <v>3</v>
       </c>
       <c r="E79" s="34" t="s">
         <v>96</v>
       </c>
-      <c r="F79" s="77"/>
-      <c r="G79" s="74"/>
-      <c r="H79" s="71"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="40"/>
+      <c r="H79" s="37"/>
     </row>
     <row r="80" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B80" s="42"/>
-      <c r="C80" s="49"/>
+      <c r="B80" s="43"/>
+      <c r="C80" s="47"/>
       <c r="D80" s="13">
         <v>4</v>
       </c>
       <c r="E80" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="F80" s="78"/>
-      <c r="G80" s="75"/>
-      <c r="H80" s="71"/>
+      <c r="F80" s="46"/>
+      <c r="G80" s="41"/>
+      <c r="H80" s="37"/>
     </row>
     <row r="81" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="42"/>
-      <c r="C81" s="49" t="s">
+      <c r="B81" s="43"/>
+      <c r="C81" s="47" t="s">
         <v>92</v>
       </c>
       <c r="D81" s="13">
@@ -3227,52 +3227,52 @@
       <c r="E81" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="F81" s="64" t="s">
+      <c r="F81" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="73" t="s">
+      <c r="G81" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="H81" s="71"/>
+      <c r="H81" s="37"/>
     </row>
     <row r="82" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="42"/>
-      <c r="C82" s="49"/>
+      <c r="B82" s="43"/>
+      <c r="C82" s="47"/>
       <c r="D82" s="13">
         <v>2</v>
       </c>
       <c r="E82" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F82" s="77"/>
-      <c r="G82" s="74"/>
-      <c r="H82" s="71"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="40"/>
+      <c r="H82" s="37"/>
     </row>
     <row r="83" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B83" s="42"/>
-      <c r="C83" s="49"/>
+      <c r="B83" s="43"/>
+      <c r="C83" s="47"/>
       <c r="D83" s="13">
         <v>3</v>
       </c>
       <c r="E83" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="F83" s="77"/>
-      <c r="G83" s="74"/>
-      <c r="H83" s="71"/>
+      <c r="F83" s="45"/>
+      <c r="G83" s="40"/>
+      <c r="H83" s="37"/>
     </row>
     <row r="84" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B84" s="42"/>
-      <c r="C84" s="49"/>
+      <c r="B84" s="43"/>
+      <c r="C84" s="47"/>
       <c r="D84" s="13">
         <v>4</v>
       </c>
       <c r="E84" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="F84" s="78"/>
-      <c r="G84" s="75"/>
-      <c r="H84" s="72"/>
+      <c r="F84" s="46"/>
+      <c r="G84" s="41"/>
+      <c r="H84" s="38"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="20"/>
@@ -3280,48 +3280,13 @@
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="H74:H84"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="G77:G80"/>
-    <mergeCell ref="G81:G84"/>
-    <mergeCell ref="B74:B84"/>
-    <mergeCell ref="F81:F84"/>
-    <mergeCell ref="F77:F80"/>
-    <mergeCell ref="F74:F76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C81:C84"/>
-    <mergeCell ref="H46:H55"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="G57:G60"/>
-    <mergeCell ref="B57:B72"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="F61:F64"/>
-    <mergeCell ref="F57:F60"/>
-    <mergeCell ref="F65:F68"/>
-    <mergeCell ref="F69:F72"/>
-    <mergeCell ref="G61:G64"/>
-    <mergeCell ref="G65:G68"/>
-    <mergeCell ref="G69:G72"/>
-    <mergeCell ref="H57:H72"/>
-    <mergeCell ref="C61:C64"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="F51:F55"/>
-    <mergeCell ref="G51:G55"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="G46:G50"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="B26:B44"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H11:H24"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="G5:G9"/>
     <mergeCell ref="B11:B24"/>
     <mergeCell ref="H26:H44"/>
     <mergeCell ref="G26:G30"/>
@@ -3338,13 +3303,48 @@
     <mergeCell ref="C11:C15"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="G16:G20"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="F5:F9"/>
-    <mergeCell ref="G5:G9"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H11:H24"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C35:C39"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="F46:F50"/>
+    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="B26:B44"/>
+    <mergeCell ref="H46:H55"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="B57:B72"/>
+    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="F65:F68"/>
+    <mergeCell ref="F69:F72"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="G65:G68"/>
+    <mergeCell ref="G69:G72"/>
+    <mergeCell ref="H57:H72"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="H74:H84"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="G77:G80"/>
+    <mergeCell ref="G81:G84"/>
+    <mergeCell ref="B74:B84"/>
+    <mergeCell ref="F81:F84"/>
+    <mergeCell ref="F77:F80"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="C81:C84"/>
   </mergeCells>
   <conditionalFormatting sqref="F5">
     <cfRule type="containsText" dxfId="53" priority="68" operator="containsText" text="MEDIUM">

--- a/Documentacion/Hsitorias_Usuario.xlsx
+++ b/Documentacion/Hsitorias_Usuario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/50178dff44962c00/Escritorio/Software_Inventario/Documentacion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1E001CD-8304-4A40-8CD4-4E04C7C10C38}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{18B6453A-4478-4620-92C1-C6ED26A0669A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{885AE308-0940-4494-9C9F-AAA8CA6AAC03}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -693,7 +693,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -732,9 +732,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -796,6 +793,108 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -817,113 +916,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1691,32 +1688,32 @@
     </row>
     <row r="3" spans="1:14" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="76"/>
-      <c r="G3" s="76"/>
-      <c r="H3" s="76"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
     </row>
     <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="77" t="s">
+      <c r="D4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="77"/>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="36"/>
+      <c r="F4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>4</v>
       </c>
       <c r="I4" s="1"/>
@@ -1727,25 +1724,25 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="71" t="s">
+      <c r="C5" s="38" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="13">
         <v>1</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="43" t="s">
+      <c r="F5" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="70" t="s">
+      <c r="G5" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="78" t="s">
+      <c r="H5" s="40" t="s">
         <v>105</v>
       </c>
       <c r="I5" s="1"/>
@@ -1756,17 +1753,17 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="70"/>
-      <c r="C6" s="72"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="13">
         <v>2</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="70"/>
-      <c r="H6" s="78"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="40"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1775,17 +1772,17 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="70"/>
-      <c r="C7" s="72"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="39"/>
       <c r="D7" s="13">
         <v>3</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="70"/>
-      <c r="H7" s="78"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="40"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -1794,17 +1791,17 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="70"/>
-      <c r="C8" s="72"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="39"/>
       <c r="D8" s="13">
         <v>4</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="70"/>
-      <c r="H8" s="78"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="40"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1813,17 +1810,17 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="70"/>
-      <c r="C9" s="72"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="39"/>
       <c r="D9" s="13">
         <v>5</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="70"/>
-      <c r="H9" s="78"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="40"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1832,13 +1829,13 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="21"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="20"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1847,25 +1844,25 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="69" t="s">
+      <c r="B11" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="38" t="s">
         <v>38</v>
       </c>
       <c r="D11" s="13">
         <v>1</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="43" t="s">
+      <c r="F11" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="70" t="s">
+      <c r="G11" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="55" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="1"/>
@@ -1876,17 +1873,17 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="69"/>
-      <c r="C12" s="72"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="39"/>
       <c r="D12" s="13">
         <v>2</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="67"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="56"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1895,17 +1892,17 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="69"/>
-      <c r="C13" s="72"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="39"/>
       <c r="D13" s="13">
         <v>3</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="67"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="56"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1914,17 +1911,17 @@
       <c r="N13" s="1"/>
     </row>
     <row r="14" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="69"/>
-      <c r="C14" s="72"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="39"/>
       <c r="D14" s="13">
         <v>4</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="67"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="56"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1933,17 +1930,17 @@
       <c r="N14" s="1"/>
     </row>
     <row r="15" spans="1:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="69"/>
-      <c r="C15" s="72"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="39"/>
       <c r="D15" s="13">
         <v>5</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="70"/>
-      <c r="H15" s="67"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="56"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1952,23 +1949,23 @@
       <c r="N15" s="1"/>
     </row>
     <row r="16" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="69"/>
-      <c r="C16" s="71" t="s">
+      <c r="B16" s="42"/>
+      <c r="C16" s="38" t="s">
         <v>108</v>
       </c>
       <c r="D16" s="13">
         <v>1</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="73" t="s">
+      <c r="G16" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="67"/>
+      <c r="H16" s="56"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1977,17 +1974,17 @@
       <c r="N16" s="1"/>
     </row>
     <row r="17" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="69"/>
-      <c r="C17" s="71"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="38"/>
       <c r="D17" s="13">
         <v>2</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="67"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="56"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1996,17 +1993,17 @@
       <c r="N17" s="1"/>
     </row>
     <row r="18" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="69"/>
-      <c r="C18" s="71"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="38"/>
       <c r="D18" s="13">
         <v>3</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="43"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="67"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="56"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -2015,17 +2012,17 @@
       <c r="N18" s="1"/>
     </row>
     <row r="19" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="69"/>
-      <c r="C19" s="71"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="38"/>
       <c r="D19" s="13">
         <v>4</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="67"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="56"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -2034,17 +2031,17 @@
       <c r="N19" s="1"/>
     </row>
     <row r="20" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="69"/>
-      <c r="C20" s="71"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="38"/>
       <c r="D20" s="13">
         <v>5</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="67"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="56"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -2053,23 +2050,23 @@
       <c r="N20" s="1"/>
     </row>
     <row r="21" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="69"/>
-      <c r="C21" s="47" t="s">
+      <c r="B21" s="42"/>
+      <c r="C21" s="48" t="s">
         <v>29</v>
       </c>
       <c r="D21" s="13">
         <v>1</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="43" t="s">
+      <c r="F21" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="63" t="s">
+      <c r="G21" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="H21" s="67"/>
+      <c r="H21" s="56"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -2078,17 +2075,17 @@
       <c r="N21" s="1"/>
     </row>
     <row r="22" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="69"/>
-      <c r="C22" s="47"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="13">
         <v>2</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="64"/>
-      <c r="H22" s="67"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="53"/>
+      <c r="H22" s="56"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -2097,17 +2094,17 @@
       <c r="N22" s="1"/>
     </row>
     <row r="23" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="69"/>
-      <c r="C23" s="47"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="13">
         <v>3</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="43"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="67"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="56"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -2116,23 +2113,23 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="2:14" ht="53.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="69"/>
+      <c r="B24" s="42"/>
       <c r="C24" s="12" t="s">
         <v>104</v>
       </c>
       <c r="D24" s="13">
         <v>1</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H24" s="68"/>
+      <c r="H24" s="57"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2141,13 +2138,13 @@
       <c r="N24" s="1"/>
     </row>
     <row r="25" spans="2:14" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="29"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="28"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
@@ -2156,25 +2153,25 @@
       <c r="N25" s="1"/>
     </row>
     <row r="26" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="48" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="13">
         <v>1</v>
       </c>
-      <c r="E26" s="34" t="s">
+      <c r="E26" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="43" t="s">
+      <c r="F26" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G26" s="61" t="s">
+      <c r="G26" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="48" t="s">
+      <c r="H26" s="43" t="s">
         <v>58</v>
       </c>
       <c r="I26" s="1"/>
@@ -2185,17 +2182,17 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:14" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="52"/>
-      <c r="C27" s="47"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="48"/>
       <c r="D27" s="13">
         <v>2</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="43"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="49"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="44"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2204,17 +2201,17 @@
       <c r="N27" s="1"/>
     </row>
     <row r="28" spans="2:14" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="52"/>
-      <c r="C28" s="47"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="13">
         <v>3</v>
       </c>
-      <c r="E28" s="34" t="s">
+      <c r="E28" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="43"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="49"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="44"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2223,30 +2220,30 @@
       <c r="N28" s="1"/>
     </row>
     <row r="29" spans="2:14" s="4" customFormat="1" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="52"/>
-      <c r="C29" s="47"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="48"/>
       <c r="D29" s="13">
         <v>4</v>
       </c>
-      <c r="E29" s="34" t="s">
+      <c r="E29" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="43"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="49"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="46"/>
+      <c r="H29" s="44"/>
     </row>
     <row r="30" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="52"/>
-      <c r="C30" s="47"/>
+      <c r="B30" s="58"/>
+      <c r="C30" s="48"/>
       <c r="D30" s="13">
         <v>5</v>
       </c>
-      <c r="E30" s="34" t="s">
+      <c r="E30" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="F30" s="43"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="49"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="44"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
@@ -2255,23 +2252,23 @@
       <c r="N30" s="1"/>
     </row>
     <row r="31" spans="2:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="52"/>
-      <c r="C31" s="47" t="s">
+      <c r="B31" s="58"/>
+      <c r="C31" s="48" t="s">
         <v>39</v>
       </c>
       <c r="D31" s="13">
         <v>1</v>
       </c>
-      <c r="E31" s="34" t="s">
+      <c r="E31" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="F31" s="43" t="s">
+      <c r="F31" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G31" s="51" t="s">
+      <c r="G31" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="49"/>
+      <c r="H31" s="44"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
@@ -2280,17 +2277,17 @@
       <c r="N31" s="1"/>
     </row>
     <row r="32" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B32" s="52"/>
-      <c r="C32" s="47"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="48"/>
       <c r="D32" s="13">
         <v>2</v>
       </c>
-      <c r="E32" s="34" t="s">
+      <c r="E32" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="F32" s="43"/>
-      <c r="G32" s="51"/>
-      <c r="H32" s="49"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="44"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -2299,17 +2296,17 @@
       <c r="N32" s="1"/>
     </row>
     <row r="33" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B33" s="52"/>
-      <c r="C33" s="47"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="48"/>
       <c r="D33" s="13">
         <v>3</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="F33" s="43"/>
-      <c r="G33" s="51"/>
-      <c r="H33" s="49"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="44"/>
       <c r="I33" s="1"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -2318,17 +2315,17 @@
       <c r="N33" s="1"/>
     </row>
     <row r="34" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B34" s="52"/>
-      <c r="C34" s="47"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="13">
         <v>4</v>
       </c>
-      <c r="E34" s="34" t="s">
+      <c r="E34" s="33" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="43"/>
-      <c r="G34" s="51"/>
-      <c r="H34" s="49"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="47"/>
+      <c r="H34" s="44"/>
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
@@ -2337,23 +2334,23 @@
       <c r="N34" s="1"/>
     </row>
     <row r="35" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="52"/>
-      <c r="C35" s="47" t="s">
+      <c r="B35" s="58"/>
+      <c r="C35" s="48" t="s">
         <v>109</v>
       </c>
       <c r="D35" s="13">
         <v>1</v>
       </c>
-      <c r="E35" s="34" t="s">
+      <c r="E35" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="43" t="s">
+      <c r="F35" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="51" t="s">
+      <c r="G35" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="H35" s="49"/>
+      <c r="H35" s="44"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
@@ -2362,17 +2359,17 @@
       <c r="N35" s="1"/>
     </row>
     <row r="36" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B36" s="52"/>
-      <c r="C36" s="47"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="48"/>
       <c r="D36" s="13">
         <v>2</v>
       </c>
-      <c r="E36" s="34" t="s">
+      <c r="E36" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="43"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="49"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="47"/>
+      <c r="H36" s="44"/>
       <c r="I36" s="1"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -2381,17 +2378,17 @@
       <c r="N36" s="1"/>
     </row>
     <row r="37" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B37" s="52"/>
-      <c r="C37" s="47"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="48"/>
       <c r="D37" s="13">
         <v>3</v>
       </c>
-      <c r="E37" s="34" t="s">
+      <c r="E37" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="43"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="49"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="44"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2400,17 +2397,17 @@
       <c r="N37" s="1"/>
     </row>
     <row r="38" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B38" s="52"/>
-      <c r="C38" s="47"/>
+      <c r="B38" s="58"/>
+      <c r="C38" s="48"/>
       <c r="D38" s="13">
         <v>4</v>
       </c>
-      <c r="E38" s="34" t="s">
+      <c r="E38" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="43"/>
-      <c r="G38" s="51"/>
-      <c r="H38" s="49"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="47"/>
+      <c r="H38" s="44"/>
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
@@ -2419,17 +2416,17 @@
       <c r="N38" s="1"/>
     </row>
     <row r="39" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B39" s="52"/>
-      <c r="C39" s="47"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="48"/>
       <c r="D39" s="13">
         <v>5</v>
       </c>
-      <c r="E39" s="34" t="s">
+      <c r="E39" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="F39" s="43"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="49"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="47"/>
+      <c r="H39" s="44"/>
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
@@ -2438,23 +2435,23 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="52"/>
-      <c r="C40" s="47" t="s">
+      <c r="B40" s="58"/>
+      <c r="C40" s="48" t="s">
         <v>40</v>
       </c>
       <c r="D40" s="13">
         <v>1</v>
       </c>
-      <c r="E40" s="34" t="s">
+      <c r="E40" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="43" t="s">
+      <c r="F40" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="51" t="s">
+      <c r="G40" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="H40" s="49"/>
+      <c r="H40" s="44"/>
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
@@ -2463,17 +2460,17 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B41" s="52"/>
-      <c r="C41" s="47"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="48"/>
       <c r="D41" s="13">
         <v>2</v>
       </c>
-      <c r="E41" s="34" t="s">
+      <c r="E41" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="43"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="49"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="44"/>
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
@@ -2482,17 +2479,17 @@
       <c r="N41" s="1"/>
     </row>
     <row r="42" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B42" s="52"/>
-      <c r="C42" s="47"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="13">
         <v>3</v>
       </c>
-      <c r="E42" s="34" t="s">
+      <c r="E42" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="43"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="49"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="47"/>
+      <c r="H42" s="44"/>
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
@@ -2501,17 +2498,17 @@
       <c r="N42" s="1"/>
     </row>
     <row r="43" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B43" s="52"/>
-      <c r="C43" s="47"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="48"/>
       <c r="D43" s="13">
         <v>4</v>
       </c>
-      <c r="E43" s="34" t="s">
+      <c r="E43" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="F43" s="43"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="49"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="44"/>
       <c r="I43" s="1"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
@@ -2520,17 +2517,17 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B44" s="52"/>
-      <c r="C44" s="47"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="48"/>
       <c r="D44" s="13">
         <v>5</v>
       </c>
-      <c r="E44" s="34" t="s">
+      <c r="E44" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="F44" s="43"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="50"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="47"/>
+      <c r="H44" s="45"/>
       <c r="I44" s="1"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -2539,13 +2536,13 @@
       <c r="N44" s="1"/>
     </row>
     <row r="45" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B45" s="24"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="29"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="28"/>
       <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
@@ -2554,25 +2551,25 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="2:14" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="52" t="s">
+      <c r="B46" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="62" t="s">
         <v>60</v>
       </c>
       <c r="D46" s="13">
         <v>1</v>
       </c>
-      <c r="E46" s="34" t="s">
+      <c r="E46" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="F46" s="43" t="s">
+      <c r="F46" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="61" t="s">
+      <c r="G46" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" s="48" t="s">
+      <c r="H46" s="43" t="s">
         <v>70</v>
       </c>
       <c r="I46" s="1"/>
@@ -2583,17 +2580,17 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B47" s="52"/>
-      <c r="C47" s="60"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="62"/>
       <c r="D47" s="13">
         <v>2</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="F47" s="43"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="49"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="46"/>
+      <c r="H47" s="44"/>
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -2602,17 +2599,17 @@
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B48" s="52"/>
-      <c r="C48" s="60"/>
+      <c r="B48" s="58"/>
+      <c r="C48" s="62"/>
       <c r="D48" s="13">
         <v>3</v>
       </c>
-      <c r="E48" s="34" t="s">
+      <c r="E48" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="F48" s="43"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="49"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="46"/>
+      <c r="H48" s="44"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2621,17 +2618,17 @@
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B49" s="52"/>
-      <c r="C49" s="60"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="62"/>
       <c r="D49" s="13">
         <v>4</v>
       </c>
-      <c r="E49" s="34" t="s">
+      <c r="E49" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="F49" s="43"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="49"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="44"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
@@ -2640,17 +2637,17 @@
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B50" s="52"/>
-      <c r="C50" s="60"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="62"/>
       <c r="D50" s="13">
         <v>5</v>
       </c>
-      <c r="E50" s="34" t="s">
+      <c r="E50" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="44"/>
-      <c r="G50" s="62"/>
-      <c r="H50" s="49"/>
+      <c r="F50" s="63"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="44"/>
       <c r="I50" s="1"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
@@ -2659,23 +2656,23 @@
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="52"/>
-      <c r="C51" s="47" t="s">
+      <c r="B51" s="58"/>
+      <c r="C51" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="18">
         <v>1</v>
       </c>
-      <c r="E51" s="14" t="s">
+      <c r="E51" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="F51" s="43" t="s">
+      <c r="F51" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="57" t="s">
+      <c r="G51" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="H51" s="49"/>
+      <c r="H51" s="44"/>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
@@ -2684,17 +2681,17 @@
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B52" s="52"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="19">
+      <c r="B52" s="58"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="18">
         <v>2</v>
       </c>
-      <c r="E52" s="14" t="s">
+      <c r="E52" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="43"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="49"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="60"/>
+      <c r="H52" s="44"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
@@ -2703,17 +2700,17 @@
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B53" s="52"/>
-      <c r="C53" s="47"/>
-      <c r="D53" s="19">
+      <c r="B53" s="58"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="18">
         <v>3</v>
       </c>
-      <c r="E53" s="14" t="s">
+      <c r="E53" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="F53" s="43"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="49"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="60"/>
+      <c r="H53" s="44"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -2722,17 +2719,17 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B54" s="52"/>
-      <c r="C54" s="47"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="48"/>
       <c r="D54" s="13">
         <v>4</v>
       </c>
-      <c r="E54" s="14" t="s">
+      <c r="E54" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="F54" s="43"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="49"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="44"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -2741,17 +2738,17 @@
       <c r="N54" s="1"/>
     </row>
     <row r="55" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="52"/>
-      <c r="C55" s="47"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="48"/>
       <c r="D55" s="13">
         <v>5</v>
       </c>
-      <c r="E55" s="14" t="s">
+      <c r="E55" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="F55" s="43"/>
-      <c r="G55" s="59"/>
-      <c r="H55" s="50"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="61"/>
+      <c r="H55" s="45"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
@@ -2760,13 +2757,13 @@
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="2:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B56" s="24"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="29"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="24"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="28"/>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
@@ -2775,25 +2772,25 @@
       <c r="N56" s="1"/>
     </row>
     <row r="57" spans="2:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="52" t="s">
+      <c r="B57" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="C57" s="47" t="s">
+      <c r="C57" s="48" t="s">
         <v>72</v>
       </c>
       <c r="D57" s="13">
         <v>1</v>
       </c>
-      <c r="E57" s="34" t="s">
+      <c r="E57" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="F57" s="53" t="s">
+      <c r="F57" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="G57" s="51" t="s">
+      <c r="G57" s="47" t="s">
         <v>34</v>
       </c>
-      <c r="H57" s="56" t="s">
+      <c r="H57" s="68" t="s">
         <v>88</v>
       </c>
       <c r="I57" s="1"/>
@@ -2804,17 +2801,17 @@
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="52"/>
-      <c r="C58" s="47"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="48"/>
       <c r="D58" s="13">
         <v>2</v>
       </c>
-      <c r="E58" s="34" t="s">
+      <c r="E58" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="F58" s="54"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="56"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="47"/>
+      <c r="H58" s="68"/>
       <c r="I58" s="1"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
@@ -2823,17 +2820,17 @@
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="2:14" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="52"/>
-      <c r="C59" s="47"/>
+      <c r="B59" s="58"/>
+      <c r="C59" s="48"/>
       <c r="D59" s="13">
         <v>3</v>
       </c>
-      <c r="E59" s="34" t="s">
+      <c r="E59" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="F59" s="54"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="56"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="47"/>
+      <c r="H59" s="68"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
@@ -2842,17 +2839,17 @@
       <c r="N59" s="1"/>
     </row>
     <row r="60" spans="2:14" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="52"/>
-      <c r="C60" s="47"/>
+      <c r="B60" s="58"/>
+      <c r="C60" s="48"/>
       <c r="D60" s="13">
         <v>4</v>
       </c>
-      <c r="E60" s="34" t="s">
+      <c r="E60" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="F60" s="55"/>
-      <c r="G60" s="51"/>
-      <c r="H60" s="56"/>
+      <c r="F60" s="67"/>
+      <c r="G60" s="47"/>
+      <c r="H60" s="68"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
@@ -2861,23 +2858,23 @@
       <c r="N60" s="1"/>
     </row>
     <row r="61" spans="2:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="52"/>
-      <c r="C61" s="47" t="s">
+      <c r="B61" s="58"/>
+      <c r="C61" s="48" t="s">
         <v>73</v>
       </c>
       <c r="D61" s="13">
         <v>1</v>
       </c>
-      <c r="E61" s="34" t="s">
+      <c r="E61" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="F61" s="53" t="s">
+      <c r="F61" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="51" t="s">
+      <c r="G61" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="H61" s="56"/>
+      <c r="H61" s="68"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
@@ -2886,17 +2883,17 @@
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="52"/>
-      <c r="C62" s="47"/>
+      <c r="B62" s="58"/>
+      <c r="C62" s="48"/>
       <c r="D62" s="13">
         <v>2</v>
       </c>
-      <c r="E62" s="34" t="s">
+      <c r="E62" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="F62" s="54"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="56"/>
+      <c r="F62" s="66"/>
+      <c r="G62" s="47"/>
+      <c r="H62" s="68"/>
       <c r="I62" s="1"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
@@ -2905,17 +2902,17 @@
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="2:14" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="52"/>
-      <c r="C63" s="47"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="48"/>
       <c r="D63" s="13">
         <v>3</v>
       </c>
-      <c r="E63" s="34" t="s">
+      <c r="E63" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="F63" s="54"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="56"/>
+      <c r="F63" s="66"/>
+      <c r="G63" s="47"/>
+      <c r="H63" s="68"/>
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -2924,17 +2921,17 @@
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="2:14" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="52"/>
-      <c r="C64" s="47"/>
+      <c r="B64" s="58"/>
+      <c r="C64" s="48"/>
       <c r="D64" s="13">
         <v>4</v>
       </c>
-      <c r="E64" s="34" t="s">
+      <c r="E64" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="F64" s="55"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="56"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="47"/>
+      <c r="H64" s="68"/>
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
@@ -2943,23 +2940,23 @@
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="52"/>
-      <c r="C65" s="47" t="s">
+      <c r="B65" s="58"/>
+      <c r="C65" s="48" t="s">
         <v>75</v>
       </c>
       <c r="D65" s="13">
         <v>1</v>
       </c>
-      <c r="E65" s="34" t="s">
+      <c r="E65" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="F65" s="53" t="s">
+      <c r="F65" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="51" t="s">
+      <c r="G65" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="H65" s="56"/>
+      <c r="H65" s="68"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
@@ -2968,17 +2965,17 @@
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B66" s="52"/>
-      <c r="C66" s="47"/>
+      <c r="B66" s="58"/>
+      <c r="C66" s="48"/>
       <c r="D66" s="13">
         <v>2</v>
       </c>
-      <c r="E66" s="34" t="s">
+      <c r="E66" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F66" s="54"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="56"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="47"/>
+      <c r="H66" s="68"/>
       <c r="I66" s="1"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
@@ -2987,17 +2984,17 @@
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B67" s="52"/>
-      <c r="C67" s="47"/>
+      <c r="B67" s="58"/>
+      <c r="C67" s="48"/>
       <c r="D67" s="13">
         <v>3</v>
       </c>
-      <c r="E67" s="34" t="s">
+      <c r="E67" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="F67" s="54"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="56"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="68"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
@@ -3006,17 +3003,17 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="52"/>
-      <c r="C68" s="47"/>
+      <c r="B68" s="58"/>
+      <c r="C68" s="48"/>
       <c r="D68" s="13">
         <v>4</v>
       </c>
-      <c r="E68" s="34" t="s">
+      <c r="E68" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="F68" s="55"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="56"/>
+      <c r="F68" s="67"/>
+      <c r="G68" s="47"/>
+      <c r="H68" s="68"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
@@ -3025,23 +3022,23 @@
       <c r="N68" s="1"/>
     </row>
     <row r="69" spans="2:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="52"/>
-      <c r="C69" s="47" t="s">
+      <c r="B69" s="58"/>
+      <c r="C69" s="48" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="13">
         <v>1</v>
       </c>
-      <c r="E69" s="34" t="s">
+      <c r="E69" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="F69" s="43" t="s">
+      <c r="F69" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="G69" s="51" t="s">
+      <c r="G69" s="47" t="s">
         <v>35</v>
       </c>
-      <c r="H69" s="56"/>
+      <c r="H69" s="68"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
@@ -3050,17 +3047,17 @@
       <c r="N69" s="1"/>
     </row>
     <row r="70" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B70" s="52"/>
-      <c r="C70" s="47"/>
+      <c r="B70" s="58"/>
+      <c r="C70" s="48"/>
       <c r="D70" s="13">
         <v>2</v>
       </c>
-      <c r="E70" s="34" t="s">
+      <c r="E70" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="F70" s="43"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="56"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="68"/>
       <c r="I70" s="1"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
@@ -3069,17 +3066,17 @@
       <c r="N70" s="1"/>
     </row>
     <row r="71" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B71" s="52"/>
-      <c r="C71" s="47"/>
+      <c r="B71" s="58"/>
+      <c r="C71" s="48"/>
       <c r="D71" s="13">
         <v>3</v>
       </c>
-      <c r="E71" s="34" t="s">
+      <c r="E71" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="F71" s="43"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="56"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="68"/>
       <c r="I71" s="1"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
@@ -3088,205 +3085,240 @@
       <c r="N71" s="1"/>
     </row>
     <row r="72" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B72" s="52"/>
-      <c r="C72" s="47"/>
+      <c r="B72" s="58"/>
+      <c r="C72" s="48"/>
       <c r="D72" s="13">
         <v>4</v>
       </c>
-      <c r="E72" s="34" t="s">
+      <c r="E72" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="F72" s="43"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="56"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="47"/>
+      <c r="H72" s="68"/>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B73" s="21"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="22"/>
-      <c r="E73" s="23"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
     </row>
     <row r="74" spans="2:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="42" t="s">
+      <c r="B74" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="C74" s="47" t="s">
+      <c r="C74" s="48" t="s">
         <v>90</v>
       </c>
       <c r="D74" s="13">
         <v>1</v>
       </c>
-      <c r="E74" s="34" t="s">
+      <c r="E74" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="F74" s="44" t="s">
+      <c r="F74" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="39" t="s">
+      <c r="G74" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="H74" s="36" t="s">
+      <c r="H74" s="69" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="75" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B75" s="43"/>
-      <c r="C75" s="47"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="48"/>
       <c r="D75" s="13">
         <v>2</v>
       </c>
-      <c r="E75" s="34" t="s">
+      <c r="E75" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="F75" s="45"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="37"/>
+      <c r="F75" s="76"/>
+      <c r="G75" s="73"/>
+      <c r="H75" s="70"/>
     </row>
     <row r="76" spans="2:14" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="B76" s="43"/>
-      <c r="C76" s="47"/>
+      <c r="B76" s="41"/>
+      <c r="C76" s="48"/>
       <c r="D76" s="13">
         <v>3</v>
       </c>
-      <c r="E76" s="34" t="s">
+      <c r="E76" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="F76" s="46"/>
-      <c r="G76" s="41"/>
-      <c r="H76" s="37"/>
+      <c r="F76" s="77"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="70"/>
     </row>
     <row r="77" spans="2:14" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="43"/>
-      <c r="C77" s="47" t="s">
+      <c r="B77" s="41"/>
+      <c r="C77" s="48" t="s">
         <v>91</v>
       </c>
       <c r="D77" s="13">
         <v>1</v>
       </c>
-      <c r="E77" s="34" t="s">
+      <c r="E77" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="F77" s="44" t="s">
+      <c r="F77" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="39" t="s">
+      <c r="G77" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="H77" s="37"/>
+      <c r="H77" s="70"/>
     </row>
     <row r="78" spans="2:14" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="43"/>
-      <c r="C78" s="47"/>
+      <c r="B78" s="41"/>
+      <c r="C78" s="48"/>
       <c r="D78" s="13">
         <v>2</v>
       </c>
-      <c r="E78" s="34" t="s">
+      <c r="E78" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="F78" s="45"/>
-      <c r="G78" s="40"/>
-      <c r="H78" s="37"/>
+      <c r="F78" s="76"/>
+      <c r="G78" s="73"/>
+      <c r="H78" s="70"/>
     </row>
     <row r="79" spans="2:14" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="43"/>
-      <c r="C79" s="47"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="48"/>
       <c r="D79" s="13">
         <v>3</v>
       </c>
-      <c r="E79" s="34" t="s">
+      <c r="E79" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="F79" s="45"/>
-      <c r="G79" s="40"/>
-      <c r="H79" s="37"/>
+      <c r="F79" s="76"/>
+      <c r="G79" s="73"/>
+      <c r="H79" s="70"/>
     </row>
     <row r="80" spans="2:14" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B80" s="43"/>
-      <c r="C80" s="47"/>
+      <c r="B80" s="41"/>
+      <c r="C80" s="48"/>
       <c r="D80" s="13">
         <v>4</v>
       </c>
-      <c r="E80" s="34" t="s">
+      <c r="E80" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="F80" s="46"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="37"/>
+      <c r="F80" s="77"/>
+      <c r="G80" s="74"/>
+      <c r="H80" s="70"/>
     </row>
     <row r="81" spans="2:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="43"/>
-      <c r="C81" s="47" t="s">
+      <c r="B81" s="41"/>
+      <c r="C81" s="48" t="s">
         <v>92</v>
       </c>
       <c r="D81" s="13">
         <v>1</v>
       </c>
-      <c r="E81" s="34" t="s">
+      <c r="E81" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="F81" s="44" t="s">
+      <c r="F81" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="39" t="s">
+      <c r="G81" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="H81" s="37"/>
+      <c r="H81" s="70"/>
     </row>
     <row r="82" spans="2:8" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="43"/>
-      <c r="C82" s="47"/>
+      <c r="B82" s="41"/>
+      <c r="C82" s="48"/>
       <c r="D82" s="13">
         <v>2</v>
       </c>
-      <c r="E82" s="34" t="s">
+      <c r="E82" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F82" s="45"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="37"/>
+      <c r="F82" s="76"/>
+      <c r="G82" s="73"/>
+      <c r="H82" s="70"/>
     </row>
     <row r="83" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B83" s="43"/>
-      <c r="C83" s="47"/>
+      <c r="B83" s="41"/>
+      <c r="C83" s="48"/>
       <c r="D83" s="13">
         <v>3</v>
       </c>
-      <c r="E83" s="34" t="s">
+      <c r="E83" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="F83" s="45"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="37"/>
+      <c r="F83" s="76"/>
+      <c r="G83" s="73"/>
+      <c r="H83" s="70"/>
     </row>
     <row r="84" spans="2:8" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="B84" s="43"/>
-      <c r="C84" s="47"/>
+      <c r="B84" s="41"/>
+      <c r="C84" s="48"/>
       <c r="D84" s="13">
         <v>4</v>
       </c>
-      <c r="E84" s="34" t="s">
+      <c r="E84" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="F84" s="46"/>
-      <c r="G84" s="41"/>
-      <c r="H84" s="38"/>
+      <c r="F84" s="77"/>
+      <c r="G84" s="74"/>
+      <c r="H84" s="71"/>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B85" s="20"/>
+      <c r="B85" s="19"/>
       <c r="C85" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="65">
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="B5:B9"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="H5:H9"/>
-    <mergeCell ref="F5:F9"/>
-    <mergeCell ref="G5:G9"/>
+    <mergeCell ref="H74:H84"/>
+    <mergeCell ref="G74:G76"/>
+    <mergeCell ref="G77:G80"/>
+    <mergeCell ref="G81:G84"/>
+    <mergeCell ref="B74:B84"/>
+    <mergeCell ref="F81:F84"/>
+    <mergeCell ref="F77:F80"/>
+    <mergeCell ref="F74:F76"/>
+    <mergeCell ref="C74:C76"/>
+    <mergeCell ref="C77:C80"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="H46:H55"/>
+    <mergeCell ref="C57:C60"/>
+    <mergeCell ref="G57:G60"/>
+    <mergeCell ref="B57:B72"/>
+    <mergeCell ref="C69:C72"/>
+    <mergeCell ref="F61:F64"/>
+    <mergeCell ref="F57:F60"/>
+    <mergeCell ref="F65:F68"/>
+    <mergeCell ref="F69:F72"/>
+    <mergeCell ref="G61:G64"/>
+    <mergeCell ref="G65:G68"/>
+    <mergeCell ref="G69:G72"/>
+    <mergeCell ref="H57:H72"/>
+    <mergeCell ref="C61:C64"/>
+    <mergeCell ref="C65:C68"/>
+    <mergeCell ref="C40:C44"/>
+    <mergeCell ref="B46:B55"/>
+    <mergeCell ref="F51:F55"/>
+    <mergeCell ref="G51:G55"/>
+    <mergeCell ref="C46:C50"/>
+    <mergeCell ref="F46:F50"/>
+    <mergeCell ref="G46:G50"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="F40:F44"/>
+    <mergeCell ref="G40:G44"/>
+    <mergeCell ref="B26:B44"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H11:H24"/>
+    <mergeCell ref="C26:C30"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="C35:C39"/>
     <mergeCell ref="B11:B24"/>
     <mergeCell ref="H26:H44"/>
     <mergeCell ref="G26:G30"/>
@@ -3303,48 +3335,13 @@
     <mergeCell ref="C11:C15"/>
     <mergeCell ref="F21:F23"/>
     <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H11:H24"/>
-    <mergeCell ref="C26:C30"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="C35:C39"/>
-    <mergeCell ref="C40:C44"/>
-    <mergeCell ref="B46:B55"/>
-    <mergeCell ref="F51:F55"/>
-    <mergeCell ref="G51:G55"/>
-    <mergeCell ref="C46:C50"/>
-    <mergeCell ref="F46:F50"/>
-    <mergeCell ref="G46:G50"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="F40:F44"/>
-    <mergeCell ref="G40:G44"/>
-    <mergeCell ref="B26:B44"/>
-    <mergeCell ref="H46:H55"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="G57:G60"/>
-    <mergeCell ref="B57:B72"/>
-    <mergeCell ref="C69:C72"/>
-    <mergeCell ref="F61:F64"/>
-    <mergeCell ref="F57:F60"/>
-    <mergeCell ref="F65:F68"/>
-    <mergeCell ref="F69:F72"/>
-    <mergeCell ref="G61:G64"/>
-    <mergeCell ref="G65:G68"/>
-    <mergeCell ref="G69:G72"/>
-    <mergeCell ref="H57:H72"/>
-    <mergeCell ref="C61:C64"/>
-    <mergeCell ref="C65:C68"/>
-    <mergeCell ref="H74:H84"/>
-    <mergeCell ref="G74:G76"/>
-    <mergeCell ref="G77:G80"/>
-    <mergeCell ref="G81:G84"/>
-    <mergeCell ref="B74:B84"/>
-    <mergeCell ref="F81:F84"/>
-    <mergeCell ref="F77:F80"/>
-    <mergeCell ref="F74:F76"/>
-    <mergeCell ref="C74:C76"/>
-    <mergeCell ref="C77:C80"/>
-    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="B5:B9"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="H5:H9"/>
+    <mergeCell ref="F5:F9"/>
+    <mergeCell ref="G5:G9"/>
   </mergeCells>
   <conditionalFormatting sqref="F5">
     <cfRule type="containsText" dxfId="53" priority="68" operator="containsText" text="MEDIUM">
